--- a/dummy_data.xlsx
+++ b/dummy_data.xlsx
@@ -448,29 +448,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>80.23</v>
+        <v>4.04</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>68.62</v>
+        <v>15.05</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -480,15 +480,15 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.08</v>
+        <v>82.87</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -498,7 +498,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.2</v>
+        <v>3.86</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -516,33 +516,33 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>93.39</v>
+        <v>6.56</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>33.18</v>
+        <v>17.95</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -552,15 +552,15 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45659</v>
+        <v>45661</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>51.01</v>
+        <v>13.36</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -570,25 +570,25 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>85.3</v>
+        <v>4.16</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>55.96</v>
+        <v>91.31</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -606,15 +606,15 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.13</v>
+        <v>10.23</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -624,15 +624,15 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3.97</v>
+        <v>1.75</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45660</v>
+        <v>45662</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37.66</v>
+        <v>14.46</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -660,15 +660,15 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45660</v>
+        <v>45662</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>42.57</v>
+        <v>16.91</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45660</v>
+        <v>45664</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>40.07</v>
+        <v>0.17</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -696,15 +696,15 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45660</v>
+        <v>45664</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19.13</v>
+        <v>8.33</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45660</v>
+        <v>45664</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>30.58</v>
+        <v>2.73</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -732,15 +732,15 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45661</v>
+        <v>45665</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12.52</v>
+        <v>16.88</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -750,15 +750,15 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45661</v>
+        <v>45665</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.74</v>
+        <v>8.85</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -768,15 +768,15 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45661</v>
+        <v>45665</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>45.01</v>
+        <v>13.19</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45661</v>
+        <v>45666</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>39.04</v>
+        <v>14.66</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45661</v>
+        <v>45666</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>54.03</v>
+        <v>17.23</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -822,15 +822,15 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45661</v>
+        <v>45667</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>41.18</v>
+        <v>0.47</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -840,33 +840,33 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45661</v>
+        <v>45667</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>81.15000000000001</v>
+        <v>11.18</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45662</v>
+        <v>45667</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>58.17</v>
+        <v>6.38</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -876,15 +876,15 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45662</v>
+        <v>45667</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11.84</v>
+        <v>0.96</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45662</v>
+        <v>45668</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25.29</v>
+        <v>18.04</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -912,15 +912,15 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45662</v>
+        <v>45668</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>64.25</v>
+        <v>94.27</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -930,15 +930,15 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45662</v>
+        <v>45669</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>44.61</v>
+        <v>10.25</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45663</v>
+        <v>45670</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37.8</v>
+        <v>8.26</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -966,33 +966,33 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45663</v>
+        <v>45670</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>92.45999999999999</v>
+        <v>1.92</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45663</v>
+        <v>45670</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>56.11</v>
+        <v>13.63</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1002,33 +1002,33 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45663</v>
+        <v>45671</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>94.40000000000001</v>
+        <v>82.87</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45663</v>
+        <v>45671</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>53.44</v>
+        <v>82.87</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1038,15 +1038,15 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45664</v>
+        <v>45671</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.72</v>
+        <v>10.31</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1056,25 +1056,25 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45664</v>
+        <v>45671</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>95.69</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45664</v>
+        <v>45672</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>79.14</v>
+        <v>14.33</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45664</v>
+        <v>45672</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>83.11</v>
+        <v>11.13</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45664</v>
+        <v>45672</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>65.05</v>
+        <v>0.06</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1128,33 +1128,33 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45665</v>
+        <v>45672</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>95.73</v>
+        <v>84.97</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45665</v>
+        <v>45672</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>42.23</v>
+        <v>90.03</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1164,15 +1164,15 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45665</v>
+        <v>45673</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>15.35</v>
+        <v>8.26</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1182,15 +1182,15 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45665</v>
+        <v>45673</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>12.21</v>
+        <v>16.54</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1200,15 +1200,15 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45665</v>
+        <v>45673</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7.59</v>
+        <v>17.6</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45665</v>
+        <v>45674</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>32.05</v>
+        <v>12.68</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1236,15 +1236,15 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45665</v>
+        <v>45675</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>42.09</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45665</v>
+        <v>45675</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1262,17 +1262,17 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>81.02</v>
+        <v>4.4</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45665</v>
+        <v>45677</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1280,43 +1280,43 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>85.65000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45665</v>
+        <v>45677</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>88.73999999999999</v>
+        <v>18.32</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45665</v>
+        <v>45677</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3.03</v>
+        <v>12.36</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45666</v>
+        <v>45678</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1334,25 +1334,25 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>90.23999999999999</v>
+        <v>96.05</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45666</v>
+        <v>45678</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>42.02</v>
+        <v>5.66</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1362,15 +1362,15 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45666</v>
+        <v>45679</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>45.54</v>
+        <v>12.82</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1380,15 +1380,15 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45666</v>
+        <v>45679</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>37.31</v>
+        <v>11.41</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1398,15 +1398,15 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45666</v>
+        <v>45679</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>50.33</v>
+        <v>7.2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1416,15 +1416,15 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45666</v>
+        <v>45679</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>79.97</v>
+        <v>82.19</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1434,15 +1434,15 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45667</v>
+        <v>45679</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>57.73</v>
+        <v>19.1</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1452,15 +1452,15 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45667</v>
+        <v>45680</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3.73</v>
+        <v>6.28</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1470,15 +1470,15 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45667</v>
+        <v>45680</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>9.6</v>
+        <v>9.02</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1488,15 +1488,15 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45667</v>
+        <v>45680</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>52.84</v>
+        <v>15.15</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1506,15 +1506,15 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45667</v>
+        <v>45681</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>48.95</v>
+        <v>19</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1524,15 +1524,15 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45667</v>
+        <v>45681</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>79.87</v>
+        <v>95.28</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1542,15 +1542,15 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45667</v>
+        <v>45682</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>11.38</v>
+        <v>12.34</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1560,15 +1560,15 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45667</v>
+        <v>45682</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3.92</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -1578,15 +1578,15 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45667</v>
+        <v>45683</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>42.62</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -1596,15 +1596,15 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45667</v>
+        <v>45683</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>18.91</v>
+        <v>11.24</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45667</v>
+        <v>45683</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -1622,17 +1622,17 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>89.65000000000001</v>
+        <v>7.44</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>45667</v>
+        <v>45683</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>13.68</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -1650,25 +1650,25 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>45667</v>
+        <v>45683</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>80.90000000000001</v>
+        <v>18.91</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>45667</v>
+        <v>45684</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -1676,17 +1676,17 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>86.01000000000001</v>
+        <v>19.05</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>45667</v>
+        <v>45685</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -1694,17 +1694,17 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>89.28</v>
+        <v>6.98</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>45668</v>
+        <v>45685</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>74.87</v>
+        <v>18.32</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -1722,43 +1722,43 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>45668</v>
+        <v>45685</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>85.06</v>
+        <v>16.36</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>45668</v>
+        <v>45685</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>89.16</v>
+        <v>7.85</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>45668</v>
+        <v>45686</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>42.28</v>
+        <v>17.95</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -1776,25 +1776,25 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>45668</v>
+        <v>45687</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>90.09999999999999</v>
+        <v>15.59</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>45668</v>
+        <v>45687</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>61.61</v>
+        <v>6.81</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -1812,15 +1812,15 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>45668</v>
+        <v>45687</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>72.48</v>
+        <v>7.08</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>45668</v>
+        <v>45688</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>70.78</v>
+        <v>6.13</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -1848,15 +1848,15 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>45668</v>
+        <v>45688</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>26.66</v>
+        <v>18.81</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -1866,15 +1866,15 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>45669</v>
+        <v>45689</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>56</v>
+        <v>18.3</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>45669</v>
+        <v>45689</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -1892,43 +1892,43 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>84.45</v>
+        <v>95.38</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>45669</v>
+        <v>45689</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>95.12</v>
+        <v>17.92</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>45669</v>
+        <v>45689</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>66.89</v>
+        <v>6.79</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -1938,15 +1938,15 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>45669</v>
+        <v>45690</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.79</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -1956,15 +1956,15 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>45669</v>
+        <v>45691</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>65.97</v>
+        <v>0.26</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -1974,15 +1974,15 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>45669</v>
+        <v>45692</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>29.17</v>
+        <v>5.05</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>45669</v>
+        <v>45692</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>8.619999999999999</v>
+        <v>12.36</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>45669</v>
+        <v>45692</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -2018,25 +2018,25 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>91.76000000000001</v>
+        <v>81.95</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>45670</v>
+        <v>45693</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>15.63</v>
+        <v>8.1</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2046,15 +2046,15 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>45670</v>
+        <v>45693</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>29.86</v>
+        <v>10.24</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>45670</v>
+        <v>45694</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -2072,25 +2072,25 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>94.81</v>
+        <v>6.81</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>45670</v>
+        <v>45694</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>63.77</v>
+        <v>86</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -2100,15 +2100,15 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>45670</v>
+        <v>45695</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>18.13</v>
+        <v>4.4</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2118,15 +2118,15 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>45670</v>
+        <v>45695</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>20.46</v>
+        <v>15.77</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>45670</v>
+        <v>45695</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5.77</v>
+        <v>17.69</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -2154,33 +2154,33 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>45670</v>
+        <v>45695</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>90.73999999999999</v>
+        <v>16.89</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>45671</v>
+        <v>45695</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>36.43</v>
+        <v>6.91</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>45671</v>
+        <v>45695</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>83.64</v>
+        <v>10.31</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>45671</v>
+        <v>45695</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>70.45999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2226,15 +2226,15 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>45671</v>
+        <v>45695</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>68.02</v>
+        <v>13.17</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>45671</v>
+        <v>45695</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>68.65000000000001</v>
+        <v>90.41</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -2262,15 +2262,15 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>45671</v>
+        <v>45695</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>45.54</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>45671</v>
+        <v>45696</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>27.22</v>
+        <v>0.76</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -2298,15 +2298,15 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>45671</v>
+        <v>45696</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>63.1</v>
+        <v>4.52</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -2316,15 +2316,15 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>45671</v>
+        <v>45697</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>26.39</v>
+        <v>12.34</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -2334,15 +2334,15 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>45671</v>
+        <v>45697</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>70.2</v>
+        <v>6.81</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>45671</v>
+        <v>45697</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>54.72</v>
+        <v>17.03</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -2370,33 +2370,33 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>45671</v>
+        <v>45697</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>97.95999999999999</v>
+        <v>7.08</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>45671</v>
+        <v>45697</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>78.95</v>
+        <v>15.52</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>45671</v>
+        <v>45698</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -2414,25 +2414,25 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>93.33</v>
+        <v>88.95</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>45671</v>
+        <v>45698</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>74.42</v>
+        <v>11.24</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -2442,15 +2442,15 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>45672</v>
+        <v>45698</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>56.41</v>
+        <v>97.11</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -2460,15 +2460,15 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>45672</v>
+        <v>45698</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>27.82</v>
+        <v>14.33</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -2478,15 +2478,15 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>45672</v>
+        <v>45698</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>33.57</v>
+        <v>7.64</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -2496,15 +2496,15 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>45672</v>
+        <v>45698</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>65.33</v>
+        <v>7.52</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -2514,15 +2514,15 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>45672</v>
+        <v>45699</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>8.58</v>
+        <v>11.77</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -2532,15 +2532,15 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>45672</v>
+        <v>45699</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>14.58</v>
+        <v>14.14</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -2550,15 +2550,15 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>45673</v>
+        <v>45699</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>56.42</v>
+        <v>11.88</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>45673</v>
+        <v>45701</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>59.51</v>
+        <v>10.7</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>45673</v>
+        <v>45701</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>24.6</v>
+        <v>4.24</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -2604,15 +2604,15 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>45673</v>
+        <v>45701</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>65.79000000000001</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -2622,15 +2622,15 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>45673</v>
+        <v>45701</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>73.70999999999999</v>
+        <v>2.84</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -2640,15 +2640,15 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>45673</v>
+        <v>45701</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>44.62</v>
+        <v>15.24</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -2658,15 +2658,15 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>45673</v>
+        <v>45702</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>77.09</v>
+        <v>15.98</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -2676,51 +2676,51 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>45673</v>
+        <v>45703</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>86.48999999999999</v>
+        <v>95.33</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>45674</v>
+        <v>45703</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>87.89</v>
+        <v>81.22</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>45674</v>
+        <v>45703</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>64.31999999999999</v>
+        <v>91.84</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -2730,15 +2730,15 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>45674</v>
+        <v>45704</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>50.98</v>
+        <v>6.91</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>45674</v>
+        <v>45704</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -2756,25 +2756,25 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>82.06999999999999</v>
+        <v>14.12</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>45674</v>
+        <v>45704</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0.96</v>
+        <v>18.27</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -2784,15 +2784,15 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>45674</v>
+        <v>45705</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>42.36</v>
+        <v>19.47</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -2802,15 +2802,15 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>45674</v>
+        <v>45706</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>34.92</v>
+        <v>13.17</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>45674</v>
+        <v>45706</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>7.85</v>
+        <v>86.52</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -2838,15 +2838,15 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>45674</v>
+        <v>45707</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>22.17</v>
+        <v>5.26</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -2856,15 +2856,15 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>45674</v>
+        <v>45707</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>48.89</v>
+        <v>0.05</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -2874,15 +2874,15 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>45674</v>
+        <v>45707</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>55.21</v>
+        <v>5.51</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>45674</v>
+        <v>45708</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>6.12</v>
+        <v>83.41</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -2910,25 +2910,25 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>45674</v>
+        <v>45708</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>86.04000000000001</v>
+        <v>16.05</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>45675</v>
+        <v>45708</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -2936,25 +2936,25 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>94.59</v>
+        <v>7.3</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>45675</v>
+        <v>45708</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>40.16</v>
+        <v>8.1</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -2964,51 +2964,51 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>45675</v>
+        <v>45708</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>94.88</v>
+        <v>10.28</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>45676</v>
+        <v>45708</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>94.16</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>45676</v>
+        <v>45709</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>36.82</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -3018,15 +3018,15 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>45676</v>
+        <v>45710</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>21.33</v>
+        <v>10.25</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -3036,15 +3036,15 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>45676</v>
+        <v>45710</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>35.94</v>
+        <v>13.89</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>45676</v>
+        <v>45710</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>37.15</v>
+        <v>85.72</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>45676</v>
+        <v>45711</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>29.16</v>
+        <v>10.23</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -3090,15 +3090,15 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>45676</v>
+        <v>45712</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>49.08</v>
+        <v>16.1</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -3108,15 +3108,15 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>45676</v>
+        <v>45712</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>18</v>
+        <v>10.65</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -3126,15 +3126,15 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>45676</v>
+        <v>45712</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>4.58</v>
+        <v>4.15</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -3144,15 +3144,15 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>45676</v>
+        <v>45713</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>35.11</v>
+        <v>19.13</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -3162,15 +3162,15 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>45676</v>
+        <v>45714</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>25.45</v>
+        <v>14.46</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>45676</v>
+        <v>45714</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>72.68000000000001</v>
+        <v>18.32</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -3198,15 +3198,15 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>45676</v>
+        <v>45714</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>55.08</v>
+        <v>16.26</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -3216,15 +3216,15 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>45676</v>
+        <v>45715</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>19.04</v>
+        <v>15.79</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -3234,15 +3234,15 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>45676</v>
+        <v>45715</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>34.53</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -3252,15 +3252,15 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>45677</v>
+        <v>45716</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>42.29</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>45677</v>
+        <v>45716</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>25.32</v>
+        <v>10.7</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -3288,15 +3288,15 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>45677</v>
+        <v>45716</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>4.33</v>
+        <v>15.95</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -3306,15 +3306,15 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>45677</v>
+        <v>45716</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>60</v>
+        <v>11.19</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -3324,15 +3324,15 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>45677</v>
+        <v>45717</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>4.05</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -3342,15 +3342,15 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>45677</v>
+        <v>45717</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>44.98</v>
+        <v>87.11</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -3360,33 +3360,33 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>45677</v>
+        <v>45717</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>93.66</v>
+        <v>2.15</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>45677</v>
+        <v>45717</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>29.96</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -3396,15 +3396,15 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>45677</v>
+        <v>45718</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>60.25</v>
+        <v>11.23</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -3414,15 +3414,15 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>45677</v>
+        <v>45718</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>28.42</v>
+        <v>1.01</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>45677</v>
+        <v>45719</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>61.63</v>
+        <v>17.76</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>45677</v>
+        <v>45719</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -3458,25 +3458,25 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>93.89</v>
+        <v>14.69</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>45678</v>
+        <v>45720</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>53.68</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>45678</v>
+        <v>45720</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -3494,25 +3494,25 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>82.65000000000001</v>
+        <v>19.1</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>45678</v>
+        <v>45720</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>3.92</v>
+        <v>0.29</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -3522,15 +3522,15 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>45678</v>
+        <v>45721</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>76.25</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -3540,15 +3540,15 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>45678</v>
+        <v>45721</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>30.83</v>
+        <v>10.1</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>45678</v>
+        <v>45722</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>42.34</v>
+        <v>15.59</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -3576,15 +3576,15 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>45678</v>
+        <v>45723</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>18.27</v>
+        <v>0.17</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>45678</v>
+        <v>45723</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -3602,17 +3602,17 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>80.72</v>
+        <v>10.4</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>45678</v>
+        <v>45724</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>36.91</v>
+        <v>6.27</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -3630,15 +3630,15 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>45678</v>
+        <v>45724</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>67.89</v>
+        <v>95.33</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>45678</v>
+        <v>45724</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>79.70999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>45679</v>
+        <v>45725</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>11.71</v>
+        <v>14.98</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -3684,15 +3684,15 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>45679</v>
+        <v>45725</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>77.63</v>
+        <v>5.84</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -3702,15 +3702,15 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>45679</v>
+        <v>45727</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>38.1</v>
+        <v>92.97</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -3720,15 +3720,15 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>45679</v>
+        <v>45727</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>10.88</v>
+        <v>1.74</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -3738,43 +3738,43 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>45679</v>
+        <v>45728</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>89.69</v>
+        <v>5.87</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>45679</v>
+        <v>45728</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>80.76000000000001</v>
+        <v>4.02</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>45680</v>
+        <v>45728</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>26.39</v>
+        <v>7.08</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -3792,15 +3792,15 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>45680</v>
+        <v>45728</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>10.67</v>
+        <v>1.02</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -3810,15 +3810,15 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>45680</v>
+        <v>45729</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>64.08</v>
+        <v>15.09</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -3828,15 +3828,15 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>45680</v>
+        <v>45729</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>47.14</v>
+        <v>6.97</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -3846,15 +3846,15 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>45680</v>
+        <v>45730</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>50.11</v>
+        <v>0.65</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -3864,15 +3864,15 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>45680</v>
+        <v>45730</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>64.63</v>
+        <v>10.7</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>45680</v>
+        <v>45730</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -3890,25 +3890,25 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>80.3</v>
+        <v>0.06</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>45680</v>
+        <v>45731</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>62.78</v>
+        <v>6.5</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -3918,15 +3918,15 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>45680</v>
+        <v>45731</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>68.34999999999999</v>
+        <v>7.59</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -3936,15 +3936,15 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>45680</v>
+        <v>45731</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>29.71</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -3954,15 +3954,15 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>45681</v>
+        <v>45731</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>77.59999999999999</v>
+        <v>5.17</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -3972,51 +3972,51 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>45681</v>
+        <v>45731</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>92.15000000000001</v>
+        <v>14.23</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>45681</v>
+        <v>45732</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>86.56999999999999</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>45681</v>
+        <v>45732</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>49.83</v>
+        <v>9.02</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -4026,15 +4026,15 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>45681</v>
+        <v>45732</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>73.53</v>
+        <v>9.66</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>45681</v>
+        <v>45732</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>18.99</v>
+        <v>14.02</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -4062,15 +4062,15 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>45681</v>
+        <v>45732</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>18.45</v>
+        <v>12.53</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -4080,15 +4080,15 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>45681</v>
+        <v>45732</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>58.09</v>
+        <v>15.2</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>45682</v>
+        <v>45733</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>76.03</v>
+        <v>12.17</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -4116,15 +4116,15 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>45682</v>
+        <v>45733</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>33.94</v>
+        <v>6.76</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -4134,25 +4134,25 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>45682</v>
+        <v>45734</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>83.77</v>
+        <v>12.27</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>45682</v>
+        <v>45735</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>27.66</v>
+        <v>6.5</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>45682</v>
+        <v>45735</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>19.31</v>
+        <v>14.64</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -4188,33 +4188,33 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>45682</v>
+        <v>45735</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>81.43000000000001</v>
+        <v>6.61</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>45683</v>
+        <v>45735</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>50.59</v>
+        <v>2.21</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -4224,15 +4224,15 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>45683</v>
+        <v>45736</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>10.79</v>
+        <v>12.23</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -4242,33 +4242,33 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>45683</v>
+        <v>45738</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>93.81999999999999</v>
+        <v>15.2</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>45683</v>
+        <v>45738</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>0.98</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>45683</v>
+        <v>45738</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>6.4</v>
+        <v>11.52</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -4296,25 +4296,25 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>45683</v>
+        <v>45739</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>89.09999999999999</v>
+        <v>19.4</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>45683</v>
+        <v>45739</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>37.62</v>
+        <v>6.21</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>45683</v>
+        <v>45739</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -4340,25 +4340,25 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>89.59999999999999</v>
+        <v>3.86</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>45683</v>
+        <v>45739</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>15.03</v>
+        <v>16.81</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -4368,15 +4368,15 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>45684</v>
+        <v>45740</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>76.83</v>
+        <v>88.95</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>45684</v>
+        <v>45740</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>26.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -4404,33 +4404,33 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>45684</v>
+        <v>45740</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>91.69</v>
+        <v>12.49</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>45684</v>
+        <v>45740</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>44.38</v>
+        <v>8.1</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -4440,15 +4440,15 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>45684</v>
+        <v>45741</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>44.59</v>
+        <v>7.84</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -4458,15 +4458,15 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>45684</v>
+        <v>45741</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>26.24</v>
+        <v>15.41</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -4476,15 +4476,15 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>45684</v>
+        <v>45742</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>65.17</v>
+        <v>7.2</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -4494,15 +4494,15 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>45684</v>
+        <v>45742</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>30.05</v>
+        <v>1.74</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -4512,33 +4512,33 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>45684</v>
+        <v>45743</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>87.79000000000001</v>
+        <v>86.52</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>45684</v>
+        <v>45744</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>79.09</v>
+        <v>14.18</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -4548,33 +4548,33 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>45684</v>
+        <v>45744</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>88.68000000000001</v>
+        <v>14.12</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>45685</v>
+        <v>45744</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>56.54</v>
+        <v>6.21</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -4584,15 +4584,15 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>45685</v>
+        <v>45744</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>15.26</v>
+        <v>3.09</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>45685</v>
+        <v>45745</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>23.1</v>
+        <v>98.05</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -4620,33 +4620,33 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>45685</v>
+        <v>45745</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>91.01000000000001</v>
+        <v>6.79</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>45685</v>
+        <v>45745</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>16.1</v>
+        <v>8.26</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -4656,25 +4656,25 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>45685</v>
+        <v>45746</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>86.94</v>
+        <v>1.09</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>45686</v>
+        <v>45746</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>30.34</v>
+        <v>4.94</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -4692,15 +4692,15 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>45687</v>
+        <v>45746</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>29.32</v>
+        <v>5.26</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -4710,25 +4710,25 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>45687</v>
+        <v>45746</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>94.04000000000001</v>
+        <v>5.97</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>45687</v>
+        <v>45747</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>62.87</v>
+        <v>4.15</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -4746,15 +4746,15 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>45687</v>
+        <v>45747</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>14.94</v>
+        <v>14.47</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>45687</v>
+        <v>45747</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>32.96</v>
+        <v>10.25</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -4782,15 +4782,15 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>45688</v>
+        <v>45748</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>49.88</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -4800,15 +4800,15 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>45688</v>
+        <v>45748</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>79.59999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -4818,15 +4818,15 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>45688</v>
+        <v>45748</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>22.06</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>45688</v>
+        <v>45749</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -4844,43 +4844,43 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>91.75</v>
+        <v>16.68</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>45688</v>
+        <v>45749</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>98.19</v>
+        <v>10.4</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>45688</v>
+        <v>45749</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>32.69</v>
+        <v>81.7</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -4890,15 +4890,15 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>45688</v>
+        <v>45750</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>78.45999999999999</v>
+        <v>12.24</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -4908,15 +4908,15 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>45688</v>
+        <v>45750</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>2.45</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -4926,15 +4926,15 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>45688</v>
+        <v>45751</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>54.18</v>
+        <v>6.01</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -4944,15 +4944,15 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>45688</v>
+        <v>45751</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>19.57</v>
+        <v>17.94</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -4962,15 +4962,15 @@
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>45688</v>
+        <v>45751</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>62.57</v>
+        <v>18.48</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -4980,33 +4980,33 @@
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
-        <v>45688</v>
+        <v>45752</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>91.73</v>
+        <v>12.23</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>45688</v>
+        <v>45753</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>40.02</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -5016,15 +5016,15 @@
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>45689</v>
+        <v>45754</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>11.3</v>
+        <v>17.44</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -5034,15 +5034,15 @@
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>45689</v>
+        <v>45754</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>49.25</v>
+        <v>15.6</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -5052,33 +5052,33 @@
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>45689</v>
+        <v>45754</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>97.63</v>
+        <v>7.08</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>45689</v>
+        <v>45755</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>76.87</v>
+        <v>86.95</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -5088,15 +5088,15 @@
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
-        <v>45690</v>
+        <v>45755</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>74.78</v>
+        <v>11</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -5106,33 +5106,33 @@
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
-        <v>45690</v>
+        <v>45756</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>98.18000000000001</v>
+        <v>10.55</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>45690</v>
+        <v>45756</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>69.92</v>
+        <v>98.79000000000001</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -5142,15 +5142,15 @@
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>45690</v>
+        <v>45756</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>51.51</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>45690</v>
+        <v>45756</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>17.98</v>
+        <v>3.09</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -5178,87 +5178,87 @@
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>45690</v>
+        <v>45756</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>83.64</v>
+        <v>3.25</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>45690</v>
+        <v>45757</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>83.27</v>
+        <v>10.6</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>45690</v>
+        <v>45757</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>83.77</v>
+        <v>2.6</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>45690</v>
+        <v>45757</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>83.89</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>45690</v>
+        <v>45758</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>41.87</v>
+        <v>18.97</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -5268,15 +5268,15 @@
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>45690</v>
+        <v>45758</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>10.31</v>
+        <v>3.01</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -5286,33 +5286,33 @@
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>45690</v>
+        <v>45758</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>92.33</v>
+        <v>11.18</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>45690</v>
+        <v>45758</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>77.36</v>
+        <v>10.29</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>45690</v>
+        <v>45758</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>40</v>
+        <v>16.68</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -5340,25 +5340,25 @@
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>45690</v>
+        <v>45759</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>82.45</v>
+        <v>6.52</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>45690</v>
+        <v>45759</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>34.07</v>
+        <v>15.4</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -5376,15 +5376,15 @@
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>45691</v>
+        <v>45759</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>67.89</v>
+        <v>2.61</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -5394,15 +5394,15 @@
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>45691</v>
+        <v>45759</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>13.56</v>
+        <v>1.05</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -5412,15 +5412,15 @@
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>45691</v>
+        <v>45760</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>10.02</v>
+        <v>6.02</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -5430,15 +5430,15 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>45691</v>
+        <v>45760</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>23.61</v>
+        <v>4.51</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -5448,15 +5448,15 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>45691</v>
+        <v>45760</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>69.61</v>
+        <v>82.87</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -5466,15 +5466,15 @@
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>45691</v>
+        <v>45762</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>17.03</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>45691</v>
+        <v>45763</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>64.34999999999999</v>
+        <v>18.32</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>45691</v>
+        <v>45764</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>54.36</v>
+        <v>19.1</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -5520,15 +5520,15 @@
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>45691</v>
+        <v>45764</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>37.9</v>
+        <v>14.69</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -5538,15 +5538,15 @@
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>45692</v>
+        <v>45764</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>40.69</v>
+        <v>15.41</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -5556,15 +5556,15 @@
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>45692</v>
+        <v>45764</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>76.13</v>
+        <v>8.85</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -5574,15 +5574,15 @@
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>45692</v>
+        <v>45765</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>20.35</v>
+        <v>11.13</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -5592,15 +5592,15 @@
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>45692</v>
+        <v>45765</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>13.19</v>
+        <v>12.49</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -5610,15 +5610,15 @@
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>45692</v>
+        <v>45765</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>39.38</v>
+        <v>14.23</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>45692</v>
+        <v>45766</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>9.970000000000001</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -5646,15 +5646,15 @@
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>45692</v>
+        <v>45766</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>36.65</v>
+        <v>14.23</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -5664,15 +5664,15 @@
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>45692</v>
+        <v>45766</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>73.89</v>
+        <v>1.92</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -5682,15 +5682,15 @@
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>45692</v>
+        <v>45766</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>64.45999999999999</v>
+        <v>13.19</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -5700,25 +5700,25 @@
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>45692</v>
+        <v>45767</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>96.20999999999999</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>45693</v>
+        <v>45767</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>63.9</v>
+        <v>16.26</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>45693</v>
+        <v>45767</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>34.74</v>
+        <v>3.31</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -5754,33 +5754,33 @@
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>45693</v>
+        <v>45769</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>87.70999999999999</v>
+        <v>11.63</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>45693</v>
+        <v>45769</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>4.31</v>
+        <v>7.92</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>45693</v>
+        <v>45769</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>51.66</v>
+        <v>11.17</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>45693</v>
+        <v>45770</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>67.20999999999999</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -5826,15 +5826,15 @@
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>45693</v>
+        <v>45770</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>64.39</v>
+        <v>16.61</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -5844,15 +5844,15 @@
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>45693</v>
+        <v>45770</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>78.59999999999999</v>
+        <v>15.17</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -5862,15 +5862,15 @@
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>45693</v>
+        <v>45770</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>51.3</v>
+        <v>7.3</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -5880,15 +5880,15 @@
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
-        <v>45693</v>
+        <v>45770</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>18.82</v>
+        <v>0.01</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -5898,15 +5898,15 @@
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
-        <v>45694</v>
+        <v>45771</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>12.79</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -5916,15 +5916,15 @@
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
-        <v>45694</v>
+        <v>45771</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>71.14</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -5934,15 +5934,15 @@
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
-        <v>45694</v>
+        <v>45771</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>64.31</v>
+        <v>92.97</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -5952,15 +5952,15 @@
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
-        <v>45694</v>
+        <v>45771</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>14.6</v>
+        <v>2.6</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -5970,15 +5970,15 @@
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
-        <v>45694</v>
+        <v>45772</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2.06</v>
+        <v>10.93</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -5988,15 +5988,15 @@
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
-        <v>45694</v>
+        <v>45772</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>65.17</v>
+        <v>11.42</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
-        <v>45694</v>
+        <v>45772</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
@@ -6014,25 +6014,25 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>93.20999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
-        <v>45695</v>
+        <v>45772</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>28.86</v>
+        <v>80.7</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -6042,15 +6042,15 @@
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
-        <v>45695</v>
+        <v>45772</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>76.47</v>
+        <v>93.12</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -6060,15 +6060,15 @@
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
-        <v>45695</v>
+        <v>45772</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>63.84</v>
+        <v>2.21</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -6078,33 +6078,33 @@
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
-        <v>45695</v>
+        <v>45773</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>99.20999999999999</v>
+        <v>16.88</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="n">
-        <v>45695</v>
+        <v>45773</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>66.11</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -6114,15 +6114,15 @@
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
-        <v>45695</v>
+        <v>45774</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>38.5</v>
+        <v>6.94</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -6132,15 +6132,15 @@
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
-        <v>45695</v>
+        <v>45774</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>23.64</v>
+        <v>7.64</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -6150,15 +6150,15 @@
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
-        <v>45696</v>
+        <v>45775</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>36.18</v>
+        <v>14.98</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -6168,25 +6168,25 @@
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
-        <v>45696</v>
+        <v>45775</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>97.84</v>
+        <v>7.44</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
-        <v>45696</v>
+        <v>45775</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>40.77</v>
+        <v>7.58</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -6204,51 +6204,51 @@
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
-        <v>45696</v>
+        <v>45775</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>82.01000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
-        <v>45696</v>
+        <v>45776</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>99.09</v>
+        <v>10.24</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
-        <v>45696</v>
+        <v>45776</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>60.19</v>
+        <v>16.18</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
-        <v>45696</v>
+        <v>45777</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>46.79</v>
+        <v>11.13</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -6276,15 +6276,15 @@
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
-        <v>45696</v>
+        <v>45777</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>30.33</v>
+        <v>17.94</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
-        <v>45696</v>
+        <v>45777</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>29.86</v>
+        <v>7.58</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -6312,15 +6312,15 @@
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
-        <v>45696</v>
+        <v>45777</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>1.42</v>
+        <v>6.43</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -6330,15 +6330,15 @@
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
-        <v>45696</v>
+        <v>45777</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>35.15</v>
+        <v>12.94</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -6348,15 +6348,15 @@
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
-        <v>45696</v>
+        <v>45778</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>9.26</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -6366,25 +6366,25 @@
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
-        <v>45696</v>
+        <v>45778</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>85.59999999999999</v>
+        <v>16.84</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
-        <v>45697</v>
+        <v>45778</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
@@ -6392,35 +6392,35 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>90.58</v>
+        <v>4.07</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
-        <v>45697</v>
+        <v>45778</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>99.34999999999999</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
-        <v>45697</v>
+        <v>45779</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>62.17</v>
+        <v>19.4</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -6438,15 +6438,15 @@
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
-        <v>45697</v>
+        <v>45779</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>37.33</v>
+        <v>80.12</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
-        <v>45697</v>
+        <v>45779</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>67.52</v>
+        <v>97.92</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
-        <v>45697</v>
+        <v>45779</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
@@ -6482,43 +6482,43 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>81.93000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
-        <v>45697</v>
+        <v>45779</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>99.38</v>
+        <v>5.61</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
-        <v>45697</v>
+        <v>45780</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>24.4</v>
+        <v>13.3</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -6528,25 +6528,25 @@
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
-        <v>45697</v>
+        <v>45781</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>82.28</v>
+        <v>81.22</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
-        <v>45697</v>
+        <v>45781</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>30.56</v>
+        <v>18.32</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -6564,15 +6564,15 @@
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
-        <v>45698</v>
+        <v>45781</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>42.82</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -6582,15 +6582,15 @@
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
-        <v>45698</v>
+        <v>45782</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>61.94</v>
+        <v>12.23</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
-        <v>45698</v>
+        <v>45782</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>75.83</v>
+        <v>3.64</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
-        <v>45698</v>
+        <v>45782</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>46.9</v>
+        <v>12.06</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -6636,15 +6636,15 @@
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
-        <v>45698</v>
+        <v>45782</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>55.37</v>
+        <v>81.22</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
-        <v>45698</v>
+        <v>45783</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>53.4</v>
+        <v>12.36</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -6672,15 +6672,15 @@
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
-        <v>45698</v>
+        <v>45783</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>73.06999999999999</v>
+        <v>18.58</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -6690,15 +6690,15 @@
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
-        <v>45699</v>
+        <v>45783</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>47.09</v>
+        <v>87.84</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -6708,25 +6708,25 @@
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
-        <v>45699</v>
+        <v>45784</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>84.12</v>
+        <v>14.69</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
-        <v>45699</v>
+        <v>45784</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>68.68000000000001</v>
+        <v>15.07</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -6744,33 +6744,33 @@
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
-        <v>45699</v>
+        <v>45785</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>80.43000000000001</v>
+        <v>10.24</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
-        <v>45699</v>
+        <v>45785</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>39.9</v>
+        <v>17.95</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -6780,15 +6780,15 @@
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
-        <v>45699</v>
+        <v>45785</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>63.41</v>
+        <v>16.89</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -6798,25 +6798,25 @@
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
-        <v>45699</v>
+        <v>45786</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>91.44</v>
+        <v>95.38</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
-        <v>45699</v>
+        <v>45787</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>56.21</v>
+        <v>6.27</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
-        <v>45700</v>
+        <v>45787</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>10.53</v>
+        <v>18.47</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
-        <v>45700</v>
+        <v>45788</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
@@ -6860,25 +6860,25 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>88.90000000000001</v>
+        <v>10.25</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
-        <v>45700</v>
+        <v>45788</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>63.44</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
-        <v>45700</v>
+        <v>45790</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
@@ -6896,25 +6896,25 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>90.19</v>
+        <v>6.88</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
-        <v>45700</v>
+        <v>45790</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>11.94</v>
+        <v>6.97</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -6924,15 +6924,15 @@
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
-        <v>45700</v>
+        <v>45790</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>66.40000000000001</v>
+        <v>6.52</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -6942,15 +6942,15 @@
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
-        <v>45700</v>
+        <v>45790</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>79.31999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
-        <v>45700</v>
+        <v>45791</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>40.15</v>
+        <v>4.07</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -6978,15 +6978,15 @@
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
-        <v>45701</v>
+        <v>45791</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>43.2</v>
+        <v>14.14</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -6996,15 +6996,15 @@
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
-        <v>45701</v>
+        <v>45792</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>25.64</v>
+        <v>15.24</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -7014,15 +7014,15 @@
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
-        <v>45701</v>
+        <v>45792</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>32.28</v>
+        <v>17.6</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -7032,15 +7032,15 @@
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
-        <v>45701</v>
+        <v>45792</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>30.92</v>
+        <v>16.84</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -7050,15 +7050,15 @@
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
-        <v>45701</v>
+        <v>45794</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>65.69</v>
+        <v>19.85</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -7068,33 +7068,33 @@
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
-        <v>45701</v>
+        <v>45794</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>84.8</v>
+        <v>0.65</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
-        <v>45701</v>
+        <v>45794</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>33.02</v>
+        <v>12.73</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -7104,33 +7104,33 @@
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
-        <v>45701</v>
+        <v>45795</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>82.70999999999999</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
-        <v>45702</v>
+        <v>45796</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>39.2</v>
+        <v>13.36</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -7140,15 +7140,15 @@
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
-        <v>45702</v>
+        <v>45796</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>32.58</v>
+        <v>94.3</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -7158,15 +7158,15 @@
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
-        <v>45702</v>
+        <v>45796</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>34.1</v>
+        <v>16.36</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -7176,33 +7176,33 @@
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
-        <v>45702</v>
+        <v>45796</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>81.70999999999999</v>
+        <v>18.91</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
-        <v>45702</v>
+        <v>45796</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>15.6</v>
+        <v>3.25</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -7212,15 +7212,15 @@
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
-        <v>45702</v>
+        <v>45797</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>32.02</v>
+        <v>15.06</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -7230,15 +7230,15 @@
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
-        <v>45702</v>
+        <v>45797</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>70.5</v>
+        <v>15.17</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
-        <v>45702</v>
+        <v>45798</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>21.38</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
-        <v>45703</v>
+        <v>45798</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>40.17</v>
+        <v>0.16</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
-        <v>45703</v>
+        <v>45799</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>72.37</v>
+        <v>1.92</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
-        <v>45703</v>
+        <v>45799</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
@@ -7310,25 +7310,25 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>83.09999999999999</v>
+        <v>12.49</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
-        <v>45703</v>
+        <v>45800</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>47.23</v>
+        <v>81.55</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
-        <v>45703</v>
+        <v>45800</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>25.07</v>
+        <v>18.81</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -7356,15 +7356,15 @@
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
-        <v>45703</v>
+        <v>45801</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>68.90000000000001</v>
+        <v>90.03</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -7374,15 +7374,15 @@
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
-        <v>45703</v>
+        <v>45801</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>37.67</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -7392,15 +7392,15 @@
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
-        <v>45703</v>
+        <v>45802</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>70.75</v>
+        <v>14.19</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -7410,15 +7410,15 @@
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
-        <v>45703</v>
+        <v>45802</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>33.07</v>
+        <v>7.08</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -7428,15 +7428,15 @@
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
-        <v>45703</v>
+        <v>45802</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>36.07</v>
+        <v>11</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -7446,15 +7446,15 @@
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
-        <v>45704</v>
+        <v>45802</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>51.73</v>
+        <v>2.79</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
-        <v>45704</v>
+        <v>45802</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>13.27</v>
+        <v>16.81</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
-        <v>45704</v>
+        <v>45803</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>42.79</v>
+        <v>6.88</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -7500,15 +7500,15 @@
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
-        <v>45704</v>
+        <v>45804</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>50.73</v>
+        <v>11.55</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -7518,33 +7518,33 @@
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
-        <v>45704</v>
+        <v>45804</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>94.23</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
-        <v>45704</v>
+        <v>45804</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>71.87</v>
+        <v>10.61</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -7554,15 +7554,15 @@
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
-        <v>45704</v>
+        <v>45805</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>65.06</v>
+        <v>3.08</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -7572,15 +7572,15 @@
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
-        <v>45705</v>
+        <v>45805</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>13.66</v>
+        <v>12.17</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -7590,15 +7590,15 @@
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
-        <v>45705</v>
+        <v>45806</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>32.97</v>
+        <v>7.64</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
-        <v>45705</v>
+        <v>45806</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>78.11</v>
+        <v>16.98</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
-        <v>45705</v>
+        <v>45806</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
@@ -7634,17 +7634,17 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>87.78</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
-        <v>45705</v>
+        <v>45807</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
@@ -7652,133 +7652,133 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>66.23</v>
+        <v>83.98</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
-        <v>45705</v>
+        <v>45808</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>72.8</v>
+        <v>11.94</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
-        <v>45705</v>
+        <v>45808</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>20.38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
-        <v>45705</v>
+        <v>45808</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C405" t="n">
-        <v>76.34999999999999</v>
+        <v>14.12</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
-        <v>45706</v>
+        <v>45808</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>52.99</v>
+        <v>6.97</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
-        <v>45706</v>
+        <v>45808</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>9.619999999999999</v>
+        <v>10.14</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
-        <v>45706</v>
+        <v>45809</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>91.43000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
-        <v>45706</v>
+        <v>45810</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>87.59999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -7788,25 +7788,25 @@
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
-        <v>45706</v>
+        <v>45810</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>77.88</v>
+        <v>14.18</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
-        <v>45706</v>
+        <v>45810</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
@@ -7814,17 +7814,17 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>33.34</v>
+        <v>12.23</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
-        <v>45706</v>
+        <v>45810</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
@@ -7832,17 +7832,17 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>73.7</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
-        <v>45706</v>
+        <v>45810</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
@@ -7850,53 +7850,53 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>68.20999999999999</v>
+        <v>17.76</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
-        <v>45706</v>
+        <v>45810</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>17.05</v>
+        <v>6.52</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
-        <v>45706</v>
+        <v>45811</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C415" t="n">
-        <v>41.89</v>
+        <v>19.47</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="1" t="n">
-        <v>45707</v>
+        <v>45811</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
@@ -7904,43 +7904,43 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>49.84</v>
+        <v>14.19</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="1" t="n">
-        <v>45707</v>
+        <v>45811</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>25.26</v>
+        <v>16.1</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="1" t="n">
-        <v>45707</v>
+        <v>45811</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>84.73999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
     </row>
     <row r="419">
       <c r="A419" s="1" t="n">
-        <v>45707</v>
+        <v>45811</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>80.29000000000001</v>
+        <v>11.67</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -7968,159 +7968,159 @@
     </row>
     <row r="420">
       <c r="A420" s="1" t="n">
-        <v>45707</v>
+        <v>45811</v>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>1.81</v>
+        <v>3.64</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="1" t="n">
-        <v>45708</v>
+        <v>45811</v>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>47.53</v>
+        <v>84.12</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="1" t="n">
-        <v>45708</v>
+        <v>45811</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>4</v>
+        <v>6.42</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="1" t="n">
-        <v>45708</v>
+        <v>45812</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C423" t="n">
-        <v>68.26000000000001</v>
+        <v>13.36</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="1" t="n">
-        <v>45708</v>
+        <v>45812</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>48.9</v>
+        <v>14.98</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="1" t="n">
-        <v>45708</v>
+        <v>45812</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>40.8</v>
+        <v>98.05</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="1" t="n">
-        <v>45708</v>
+        <v>45812</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>40.19</v>
+        <v>17.2</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="1" t="n">
-        <v>45708</v>
+        <v>45812</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>54.06</v>
+        <v>16.54</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="1" t="n">
-        <v>45709</v>
+        <v>45813</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>82.42</v>
+        <v>97.11</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -8130,25 +8130,25 @@
     </row>
     <row r="429">
       <c r="A429" s="1" t="n">
-        <v>45709</v>
+        <v>45813</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>74.98999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="1" t="n">
-        <v>45709</v>
+        <v>45814</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
@@ -8156,17 +8156,17 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>7.53</v>
+        <v>14.73</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="1" t="n">
-        <v>45709</v>
+        <v>45814</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
@@ -8174,43 +8174,43 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>3.39</v>
+        <v>89.84</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="1" t="n">
-        <v>45710</v>
+        <v>45814</v>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C432" t="n">
-        <v>43.64</v>
+        <v>16.68</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="1" t="n">
-        <v>45710</v>
+        <v>45814</v>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>84.40000000000001</v>
+        <v>19.47</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -8220,61 +8220,61 @@
     </row>
     <row r="434">
       <c r="A434" s="1" t="n">
-        <v>45710</v>
+        <v>45815</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>77.58</v>
+        <v>12.49</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="1" t="n">
-        <v>45710</v>
+        <v>45815</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C435" t="n">
-        <v>61.63</v>
+        <v>7.92</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="1" t="n">
-        <v>45710</v>
+        <v>45816</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C436" t="n">
-        <v>32.32</v>
+        <v>11.55</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="1" t="n">
-        <v>45710</v>
+        <v>45816</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
@@ -8282,35 +8282,35 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>49.07</v>
+        <v>19</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="1" t="n">
-        <v>45710</v>
+        <v>45816</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>14.71</v>
+        <v>10.65</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="1" t="n">
-        <v>45710</v>
+        <v>45817</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
@@ -8318,89 +8318,89 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>17.67</v>
+        <v>17.95</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="1" t="n">
-        <v>45710</v>
+        <v>45817</v>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>19.99</v>
+        <v>16.54</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="1" t="n">
-        <v>45710</v>
+        <v>45817</v>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C441" t="n">
-        <v>43.29</v>
+        <v>81.95</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="1" t="n">
-        <v>45711</v>
+        <v>45818</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C442" t="n">
-        <v>45.68</v>
+        <v>5.51</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="1" t="n">
-        <v>45711</v>
+        <v>45818</v>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C443" t="n">
-        <v>26.59</v>
+        <v>18.92</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="1" t="n">
-        <v>45711</v>
+        <v>45818</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
@@ -8408,133 +8408,133 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>37.67</v>
+        <v>0.05</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="1" t="n">
-        <v>45711</v>
+        <v>45819</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>30.06</v>
+        <v>88.95</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="1" t="n">
-        <v>45711</v>
+        <v>45820</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>22.56</v>
+        <v>19.1</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="1" t="n">
-        <v>45711</v>
+        <v>45820</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C447" t="n">
-        <v>74.45</v>
+        <v>2.52</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="1" t="n">
-        <v>45711</v>
+        <v>45821</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>10.96</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="1" t="n">
-        <v>45711</v>
+        <v>45822</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C449" t="n">
-        <v>67.38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="1" t="n">
-        <v>45711</v>
+        <v>45822</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C450" t="n">
-        <v>8.550000000000001</v>
+        <v>4.02</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="1" t="n">
-        <v>45712</v>
+        <v>45822</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>85.64</v>
+        <v>10.28</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -8544,33 +8544,33 @@
     </row>
     <row r="452">
       <c r="A452" s="1" t="n">
-        <v>45712</v>
+        <v>45822</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C452" t="n">
-        <v>72.73</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="1" t="n">
-        <v>45712</v>
+        <v>45822</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C453" t="n">
-        <v>80.58</v>
+        <v>11.77</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -8580,33 +8580,33 @@
     </row>
     <row r="454">
       <c r="A454" s="1" t="n">
-        <v>45712</v>
+        <v>45822</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>68.18000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="1" t="n">
-        <v>45712</v>
+        <v>45823</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>96.90000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -8616,69 +8616,69 @@
     </row>
     <row r="456">
       <c r="A456" s="1" t="n">
-        <v>45712</v>
+        <v>45823</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C456" t="n">
-        <v>56.76</v>
+        <v>10.14</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="1" t="n">
-        <v>45712</v>
+        <v>45823</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>68.33</v>
+        <v>5.58</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="1" t="n">
-        <v>45712</v>
+        <v>45824</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>69.26000000000001</v>
+        <v>12.82</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="1" t="n">
-        <v>45713</v>
+        <v>45825</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>84.38</v>
+        <v>4.77</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -8688,43 +8688,43 @@
     </row>
     <row r="460">
       <c r="A460" s="1" t="n">
-        <v>45713</v>
+        <v>45825</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C460" t="n">
-        <v>25.05</v>
+        <v>3.03</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="1" t="n">
-        <v>45713</v>
+        <v>45825</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>62.25</v>
+        <v>16.45</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="1" t="n">
-        <v>45713</v>
+        <v>45825</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -8732,79 +8732,79 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>2.82</v>
+        <v>12.06</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="1" t="n">
-        <v>45713</v>
+        <v>45826</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>78.5</v>
+        <v>4.02</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="1" t="n">
-        <v>45713</v>
+        <v>45826</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C464" t="n">
-        <v>79.66</v>
+        <v>16.89</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="1" t="n">
-        <v>45714</v>
+        <v>45826</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>45.84</v>
+        <v>2.95</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="1" t="n">
-        <v>45714</v>
+        <v>45826</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>93.63</v>
+        <v>16.84</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
     </row>
     <row r="467">
       <c r="A467" s="1" t="n">
-        <v>45714</v>
+        <v>45826</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>89.29000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -8832,79 +8832,79 @@
     </row>
     <row r="468">
       <c r="A468" s="1" t="n">
-        <v>45714</v>
+        <v>45828</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C468" t="n">
-        <v>62.45</v>
+        <v>95.28</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="1" t="n">
-        <v>45714</v>
+        <v>45828</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>55.8</v>
+        <v>16.97</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="1" t="n">
-        <v>45714</v>
+        <v>45828</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>59</v>
+        <v>92.97</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="1" t="n">
-        <v>45714</v>
+        <v>45828</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>50.03</v>
+        <v>3.79</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="1" t="n">
-        <v>45715</v>
+        <v>45829</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
@@ -8912,17 +8912,17 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>77.12</v>
+        <v>2.07</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="1" t="n">
-        <v>45715</v>
+        <v>45830</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
@@ -8930,35 +8930,35 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>2.85</v>
+        <v>12.05</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="1" t="n">
-        <v>45715</v>
+        <v>45830</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C474" t="n">
-        <v>75.45</v>
+        <v>15.4</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="1" t="n">
-        <v>45715</v>
+        <v>45830</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
@@ -8966,17 +8966,17 @@
         </is>
       </c>
       <c r="C475" t="n">
-        <v>3.63</v>
+        <v>9.93</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="1" t="n">
-        <v>45715</v>
+        <v>45831</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
@@ -8984,143 +8984,143 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>27.46</v>
+        <v>18.91</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="1" t="n">
-        <v>45715</v>
+        <v>45832</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>69.31</v>
+        <v>4.71</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="1" t="n">
-        <v>45715</v>
+        <v>45833</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>61.07</v>
+        <v>19.4</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="1" t="n">
-        <v>45715</v>
+        <v>45833</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C479" t="n">
-        <v>0.06</v>
+        <v>4.07</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="1" t="n">
-        <v>45716</v>
+        <v>45834</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>77.69</v>
+        <v>2.95</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="1" t="n">
-        <v>45716</v>
+        <v>45834</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>57.72</v>
+        <v>18.47</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="1" t="n">
-        <v>45716</v>
+        <v>45834</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>79.41</v>
+        <v>15.06</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="1" t="n">
-        <v>45716</v>
+        <v>45835</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C483" t="n">
-        <v>33.51</v>
+        <v>3.38</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="1" t="n">
-        <v>45716</v>
+        <v>45836</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
@@ -9128,17 +9128,17 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>52.21</v>
+        <v>7.44</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="1" t="n">
-        <v>45717</v>
+        <v>45836</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>86.52</v>
+        <v>4.84</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -9156,33 +9156,33 @@
     </row>
     <row r="486">
       <c r="A486" s="1" t="n">
-        <v>45717</v>
+        <v>45836</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>5.62</v>
+        <v>13.52</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="1" t="n">
-        <v>45717</v>
+        <v>45836</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>88.93000000000001</v>
+        <v>4.14</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -9192,25 +9192,25 @@
     </row>
     <row r="488">
       <c r="A488" s="1" t="n">
-        <v>45717</v>
+        <v>45836</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>30.49</v>
+        <v>12.82</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="1" t="n">
-        <v>45717</v>
+        <v>45836</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
@@ -9218,53 +9218,53 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>5.94</v>
+        <v>13.8</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="1" t="n">
-        <v>45717</v>
+        <v>45836</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C490" t="n">
-        <v>44.59</v>
+        <v>13.19</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="1" t="n">
-        <v>45717</v>
+        <v>45836</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>73.97</v>
+        <v>11.96</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="1" t="n">
-        <v>45717</v>
+        <v>45837</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
@@ -9272,25 +9272,25 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>56.84</v>
+        <v>83.41</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="1" t="n">
-        <v>45717</v>
+        <v>45837</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C493" t="n">
-        <v>94.73999999999999</v>
+        <v>10.13</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
     </row>
     <row r="494">
       <c r="A494" s="1" t="n">
-        <v>45718</v>
+        <v>45837</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
@@ -9308,25 +9308,25 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>33.79</v>
+        <v>10.7</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="1" t="n">
-        <v>45718</v>
+        <v>45837</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C495" t="n">
-        <v>85.3</v>
+        <v>7.3</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -9336,25 +9336,25 @@
     </row>
     <row r="496">
       <c r="A496" s="1" t="n">
-        <v>45718</v>
+        <v>45837</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C496" t="n">
-        <v>74.41</v>
+        <v>16.81</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="1" t="n">
-        <v>45718</v>
+        <v>45838</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>84.31</v>
+        <v>2.84</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -9372,15 +9372,15 @@
     </row>
     <row r="498">
       <c r="A498" s="1" t="n">
-        <v>45718</v>
+        <v>45838</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C498" t="n">
-        <v>92.01000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -9390,43 +9390,43 @@
     </row>
     <row r="499">
       <c r="A499" s="1" t="n">
-        <v>45718</v>
+        <v>45838</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C499" t="n">
-        <v>79.15000000000001</v>
+        <v>10.31</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="1" t="n">
-        <v>45718</v>
+        <v>45838</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C500" t="n">
-        <v>50.08</v>
+        <v>5.05</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="1" t="n">
-        <v>45718</v>
+        <v>45838</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
@@ -9434,11 +9434,11 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>70.37</v>
+        <v>16.88</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>

--- a/dummy_data.xlsx
+++ b/dummy_data.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.04</v>
+        <v>10.33</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -462,33 +462,33 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15.05</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>82.87</v>
+        <v>13.73</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -498,15 +498,15 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45660</v>
+        <v>45659</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.86</v>
+        <v>16.67</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45660</v>
+        <v>45659</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.56</v>
+        <v>14.64</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45660</v>
+        <v>45659</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.95</v>
+        <v>6.13</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13.36</v>
+        <v>10.35</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -570,15 +570,15 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45662</v>
+        <v>45660</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4.16</v>
+        <v>10.71</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45662</v>
+        <v>45660</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91.31</v>
+        <v>19.37</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45662</v>
+        <v>45660</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10.23</v>
+        <v>6.49</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45662</v>
+        <v>45660</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.75</v>
+        <v>7.54</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -642,15 +642,15 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45662</v>
+        <v>45660</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14.46</v>
+        <v>3.03</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -664,11 +664,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.91</v>
+        <v>6.24</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.17</v>
+        <v>16.52</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -696,33 +696,33 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.33</v>
+        <v>89.12</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.73</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45665</v>
+        <v>45663</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.88</v>
+        <v>19.73</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -750,15 +750,15 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45665</v>
+        <v>45663</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.85</v>
+        <v>7.94</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45665</v>
+        <v>45663</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -776,25 +776,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13.19</v>
+        <v>91.81</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45666</v>
+        <v>45663</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>14.66</v>
+        <v>15.73</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45666</v>
+        <v>45664</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17.23</v>
+        <v>15.85</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -822,33 +822,33 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45667</v>
+        <v>45664</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.47</v>
+        <v>97.92</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45667</v>
+        <v>45665</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11.18</v>
+        <v>13.91</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -858,19 +858,19 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45667</v>
+        <v>45666</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6.38</v>
+        <v>97.72</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -880,11 +880,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.96</v>
+        <v>19.35</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -894,15 +894,15 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45668</v>
+        <v>45667</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18.04</v>
+        <v>18.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45668</v>
+        <v>45667</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>94.27</v>
+        <v>15.81</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -930,15 +930,15 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45669</v>
+        <v>45668</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10.25</v>
+        <v>2.61</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -948,15 +948,15 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45670</v>
+        <v>45668</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8.26</v>
+        <v>17.69</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -966,15 +966,15 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45670</v>
+        <v>45668</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.92</v>
+        <v>12.6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -984,33 +984,33 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45670</v>
+        <v>45669</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13.63</v>
+        <v>81.84</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45671</v>
+        <v>45669</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>82.87</v>
+        <v>3.42</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1020,15 +1020,15 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45671</v>
+        <v>45669</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>82.87</v>
+        <v>1.05</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1038,15 +1038,15 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45671</v>
+        <v>45670</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10.31</v>
+        <v>3.2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>81.40000000000001</v>
+        <v>5.12</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1074,15 +1074,15 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45672</v>
+        <v>45671</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>14.33</v>
+        <v>17.8</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45672</v>
+        <v>45671</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>11.13</v>
+        <v>90.34</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45672</v>
+        <v>45671</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.06</v>
+        <v>13.91</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1132,11 +1132,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>84.97</v>
+        <v>7.61</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1150,11 +1150,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>90.03</v>
+        <v>15.9</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1164,15 +1164,15 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45673</v>
+        <v>45675</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8.26</v>
+        <v>5.74</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1182,15 +1182,15 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45673</v>
+        <v>45675</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>16.54</v>
+        <v>14.75</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1200,15 +1200,15 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45673</v>
+        <v>45675</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>17.6</v>
+        <v>19.08</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1218,15 +1218,15 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45674</v>
+        <v>45675</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>12.68</v>
+        <v>11.02</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1236,15 +1236,15 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45675</v>
+        <v>45676</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>88.01000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1254,15 +1254,15 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45675</v>
+        <v>45676</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4.4</v>
+        <v>14.54</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1272,33 +1272,33 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45677</v>
+        <v>45676</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>19.4</v>
+        <v>93.11</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45677</v>
+        <v>45676</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>18.32</v>
+        <v>2.61</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1316,25 +1316,25 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>12.36</v>
+        <v>88.22</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45678</v>
+        <v>45677</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>96.05</v>
+        <v>17.2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45678</v>
+        <v>45677</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5.66</v>
+        <v>3.38</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1362,15 +1362,15 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45679</v>
+        <v>45677</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>12.82</v>
+        <v>13.48</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1380,15 +1380,15 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45679</v>
+        <v>45678</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>11.41</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1398,15 +1398,15 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45679</v>
+        <v>45678</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7.2</v>
+        <v>15.78</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1416,15 +1416,15 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45679</v>
+        <v>45678</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>82.19</v>
+        <v>12.6</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1438,11 +1438,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>19.1</v>
+        <v>17.8</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1452,15 +1452,15 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45680</v>
+        <v>45679</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6.28</v>
+        <v>7.72</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1470,15 +1470,15 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45680</v>
+        <v>45679</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>9.02</v>
+        <v>2.13</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1488,15 +1488,15 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45680</v>
+        <v>45679</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>15.15</v>
+        <v>16.66</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1506,15 +1506,15 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45681</v>
+        <v>45679</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>19</v>
+        <v>5.47</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1524,15 +1524,15 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45681</v>
+        <v>45680</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>95.28</v>
+        <v>0.12</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1542,15 +1542,15 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45682</v>
+        <v>45680</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>12.34</v>
+        <v>8.19</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1560,15 +1560,15 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45682</v>
+        <v>45681</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>90.18000000000001</v>
+        <v>15.78</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -1578,15 +1578,15 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45683</v>
+        <v>45681</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>84.76000000000001</v>
+        <v>15.26</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -1596,25 +1596,25 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45683</v>
+        <v>45681</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>11.24</v>
+        <v>96.98</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45683</v>
+        <v>45681</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7.44</v>
+        <v>14.21</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -1632,15 +1632,15 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>45683</v>
+        <v>45682</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>90.70999999999999</v>
+        <v>19.77</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -1650,15 +1650,15 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>45683</v>
+        <v>45682</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>18.91</v>
+        <v>15.73</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -1668,15 +1668,15 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>45684</v>
+        <v>45683</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>19.05</v>
+        <v>6.19</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -1686,15 +1686,15 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>45685</v>
+        <v>45683</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6.98</v>
+        <v>17.45</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>45685</v>
+        <v>45684</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>18.32</v>
+        <v>3.04</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -1722,51 +1722,51 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>45685</v>
+        <v>45684</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>16.36</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>45685</v>
+        <v>45684</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>7.85</v>
+        <v>81.16</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>45686</v>
+        <v>45685</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>17.95</v>
+        <v>4.54</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>45687</v>
+        <v>45685</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15.59</v>
+        <v>14.98</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -1794,15 +1794,15 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>45687</v>
+        <v>45685</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6.81</v>
+        <v>3.86</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -1812,15 +1812,15 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>45687</v>
+        <v>45686</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>7.08</v>
+        <v>5.44</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -1830,15 +1830,15 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>45688</v>
+        <v>45686</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>6.13</v>
+        <v>3.76</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -1848,15 +1848,15 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>45688</v>
+        <v>45686</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>18.81</v>
+        <v>0.42</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -1866,15 +1866,15 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>45689</v>
+        <v>45686</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>18.3</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>45689</v>
+        <v>45686</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>95.38</v>
+        <v>10.67</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>45689</v>
+        <v>45687</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>17.92</v>
+        <v>13.28</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>45689</v>
+        <v>45688</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6.79</v>
+        <v>2.25</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>45690</v>
+        <v>45689</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>94.15000000000001</v>
+        <v>18.33</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -1956,15 +1956,15 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>45691</v>
+        <v>45689</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.26</v>
+        <v>9.77</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -1974,15 +1974,15 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>45692</v>
+        <v>45689</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5.05</v>
+        <v>6.46</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -1992,15 +1992,15 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>45692</v>
+        <v>45689</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>12.36</v>
+        <v>2.61</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>45692</v>
+        <v>45690</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>81.95</v>
+        <v>15.33</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>45693</v>
+        <v>45690</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>8.1</v>
+        <v>17.43</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2046,15 +2046,15 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>45693</v>
+        <v>45690</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10.24</v>
+        <v>3.76</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>45694</v>
+        <v>45690</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>6.81</v>
+        <v>10.67</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2082,25 +2082,25 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>45694</v>
+        <v>45690</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>86</v>
+        <v>87.7</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>45695</v>
+        <v>45690</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -2108,25 +2108,25 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>4.4</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>45695</v>
+        <v>45690</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>15.77</v>
+        <v>13.57</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2136,15 +2136,15 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>45695</v>
+        <v>45691</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>17.69</v>
+        <v>14.89</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>45695</v>
+        <v>45691</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>16.89</v>
+        <v>12.37</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -2172,15 +2172,15 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>45695</v>
+        <v>45691</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6.91</v>
+        <v>17.65</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2190,15 +2190,15 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>45695</v>
+        <v>45692</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>10.31</v>
+        <v>4.35</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2208,15 +2208,15 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>45695</v>
+        <v>45692</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>9.83</v>
+        <v>4.87</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2226,15 +2226,15 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>45695</v>
+        <v>45693</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>13.17</v>
+        <v>13.51</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2244,51 +2244,51 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>45695</v>
+        <v>45693</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>90.41</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>45695</v>
+        <v>45693</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>98.43000000000001</v>
+        <v>93.92</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>45696</v>
+        <v>45693</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.76</v>
+        <v>9.75</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -2298,15 +2298,15 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>45696</v>
+        <v>45693</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4.52</v>
+        <v>13.23</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -2316,15 +2316,15 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>45697</v>
+        <v>45694</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>12.34</v>
+        <v>3.12</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -2334,15 +2334,15 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>45697</v>
+        <v>45694</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>6.81</v>
+        <v>3.86</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -2352,15 +2352,15 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>45697</v>
+        <v>45694</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>17.03</v>
+        <v>13.6</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>45697</v>
+        <v>45694</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>7.08</v>
+        <v>19.76</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -2388,51 +2388,51 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>45697</v>
+        <v>45695</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>15.52</v>
+        <v>83.05</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>45698</v>
+        <v>45695</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>88.95</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>45698</v>
+        <v>45695</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>11.24</v>
+        <v>5.47</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>45698</v>
+        <v>45696</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>97.11</v>
+        <v>6.38</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>45698</v>
+        <v>45697</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>14.33</v>
+        <v>3.86</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -2478,33 +2478,33 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>45698</v>
+        <v>45697</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>7.64</v>
+        <v>89.47</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>45698</v>
+        <v>45697</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>7.52</v>
+        <v>8.19</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>45699</v>
+        <v>45698</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>11.77</v>
+        <v>4.4</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -2532,15 +2532,15 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>45699</v>
+        <v>45698</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>14.14</v>
+        <v>7.59</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>11.88</v>
+        <v>17.03</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -2568,15 +2568,15 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>45701</v>
+        <v>45699</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>10.7</v>
+        <v>6.13</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -2586,15 +2586,15 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>45701</v>
+        <v>45700</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>4.24</v>
+        <v>19.25</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -2604,33 +2604,33 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>45701</v>
+        <v>45700</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>88.01000000000001</v>
+        <v>98.66</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>45701</v>
+        <v>45700</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2.84</v>
+        <v>9.48</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -2640,19 +2640,19 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>15.24</v>
+        <v>97.72</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>15.98</v>
+        <v>9.56</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -2676,15 +2676,15 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>45703</v>
+        <v>45704</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>95.33</v>
+        <v>12.7</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -2694,15 +2694,15 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>45703</v>
+        <v>45704</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>81.22</v>
+        <v>3.83</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -2712,15 +2712,15 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>45703</v>
+        <v>45704</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>91.84</v>
+        <v>18.2</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -2738,25 +2738,25 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>6.91</v>
+        <v>97.72</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>45704</v>
+        <v>45705</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>14.12</v>
+        <v>15.78</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>45704</v>
+        <v>45705</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>18.27</v>
+        <v>2.4</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -2788,21 +2788,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>19.47</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>45706</v>
+        <v>45705</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>13.17</v>
+        <v>9.75</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -2828,43 +2828,43 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>86.52</v>
+        <v>86.67</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>45707</v>
+        <v>45706</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>5.26</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>45707</v>
+        <v>45706</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0.05</v>
+        <v>4.98</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -2878,11 +2878,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>5.51</v>
+        <v>3.65</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -2892,15 +2892,15 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>45708</v>
+        <v>45707</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>83.41</v>
+        <v>2.32</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -2910,15 +2910,15 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>45708</v>
+        <v>45707</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>16.05</v>
+        <v>7.85</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -2928,15 +2928,15 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>45708</v>
+        <v>45707</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>7.3</v>
+        <v>19.37</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -2946,15 +2946,15 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>45708</v>
+        <v>45707</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>8.1</v>
+        <v>14.75</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -2968,11 +2968,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>10.28</v>
+        <v>10.3</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>9.039999999999999</v>
+        <v>3.86</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -3000,15 +3000,15 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>45709</v>
+        <v>45708</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>9.279999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -3018,15 +3018,15 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>45710</v>
+        <v>45709</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>10.25</v>
+        <v>5.44</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -3040,11 +3040,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>13.89</v>
+        <v>6.35</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -3058,11 +3058,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>85.72</v>
+        <v>5.81</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -3076,11 +3076,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>10.23</v>
+        <v>7.59</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -3090,15 +3090,15 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>45712</v>
+        <v>45711</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>16.1</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>45712</v>
+        <v>45711</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>10.65</v>
+        <v>19.33</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -3130,29 +3130,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>4.15</v>
+        <v>82.56</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>45713</v>
+        <v>45714</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>19.13</v>
+        <v>10.3</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>14.46</v>
+        <v>18.1</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -3188,25 +3188,25 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>18.32</v>
+        <v>87.89</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>45714</v>
+        <v>45716</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>16.26</v>
+        <v>0.62</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -3216,15 +3216,15 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>45715</v>
+        <v>45716</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>15.79</v>
+        <v>9.76</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -3234,19 +3234,19 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>45715</v>
+        <v>45716</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>94.81999999999999</v>
+        <v>89.06</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -3256,11 +3256,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>92.15000000000001</v>
+        <v>3.42</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -3270,43 +3270,43 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>45716</v>
+        <v>45717</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>10.7</v>
+        <v>90.34</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>45716</v>
+        <v>45717</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>15.95</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>45716</v>
+        <v>45717</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>11.19</v>
+        <v>13.49</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -3328,29 +3328,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>9.859999999999999</v>
+        <v>80.19</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>45717</v>
+        <v>45718</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>87.11</v>
+        <v>0.61</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -3360,15 +3360,15 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>45717</v>
+        <v>45718</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2.15</v>
+        <v>11.33</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>45717</v>
+        <v>45718</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>98.43000000000001</v>
+        <v>10.71</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -3400,15 +3400,15 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>11.23</v>
+        <v>96.11</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -3418,11 +3418,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1.01</v>
+        <v>5.15</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -3436,11 +3436,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>17.76</v>
+        <v>2.74</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -3450,15 +3450,15 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>45719</v>
+        <v>45720</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>14.69</v>
+        <v>15.73</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>45720</v>
+        <v>45721</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>94.04000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>45720</v>
+        <v>45722</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>19.1</v>
+        <v>13.31</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -3504,15 +3504,15 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>45720</v>
+        <v>45722</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>0.29</v>
+        <v>4.45</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>45721</v>
+        <v>45723</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>92.15000000000001</v>
+        <v>18.83</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -3540,15 +3540,15 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>45721</v>
+        <v>45723</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>10.1</v>
+        <v>6.19</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>45722</v>
+        <v>45724</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -3566,25 +3566,25 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>15.59</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>0.17</v>
+        <v>18.1</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -3594,15 +3594,15 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>10.4</v>
+        <v>14.48</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -3612,15 +3612,15 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>45724</v>
+        <v>45725</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>6.27</v>
+        <v>1.36</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>45724</v>
+        <v>45725</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -3638,17 +3638,17 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>95.33</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>45724</v>
+        <v>45725</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -3666,15 +3666,15 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>45725</v>
+        <v>45726</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>14.98</v>
+        <v>2.37</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -3684,15 +3684,15 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>45725</v>
+        <v>45726</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>5.84</v>
+        <v>11.84</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -3706,11 +3706,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>92.97</v>
+        <v>16.27</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -3724,11 +3724,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1.74</v>
+        <v>1.36</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -3738,33 +3738,33 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>45728</v>
+        <v>45727</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>5.87</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>45728</v>
+        <v>45727</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>4.02</v>
+        <v>9.49</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -3778,11 +3778,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>7.08</v>
+        <v>18.1</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -3796,11 +3796,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1.02</v>
+        <v>12.76</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -3810,15 +3810,15 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>45729</v>
+        <v>45728</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>15.09</v>
+        <v>8.56</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -3828,15 +3828,15 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>45729</v>
+        <v>45728</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>6.97</v>
+        <v>19.46</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -3846,15 +3846,15 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>45730</v>
+        <v>45729</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>0.65</v>
+        <v>8.43</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -3868,11 +3868,11 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>10.7</v>
+        <v>8.08</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -3882,33 +3882,33 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>45730</v>
+        <v>45731</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0.06</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>45731</v>
+        <v>45732</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>6.5</v>
+        <v>7.54</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>45731</v>
+        <v>45732</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>7.59</v>
+        <v>1.3</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -3936,15 +3936,15 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>45731</v>
+        <v>45732</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>92.81999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -3954,33 +3954,33 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>45731</v>
+        <v>45733</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>5.17</v>
+        <v>96.94</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>45731</v>
+        <v>45733</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>14.23</v>
+        <v>4.97</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>45732</v>
+        <v>45733</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>95.81999999999999</v>
+        <v>10.97</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -4008,15 +4008,15 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>45732</v>
+        <v>45733</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>9.02</v>
+        <v>12.76</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -4026,15 +4026,15 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>45732</v>
+        <v>45733</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>9.66</v>
+        <v>3.38</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -4044,15 +4044,15 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>45732</v>
+        <v>45734</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>14.02</v>
+        <v>10.67</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -4062,15 +4062,15 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>45732</v>
+        <v>45734</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>12.53</v>
+        <v>7.72</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>45732</v>
+        <v>45734</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>15.2</v>
+        <v>9.15</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -4098,15 +4098,15 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>45733</v>
+        <v>45735</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>12.17</v>
+        <v>4.83</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>45733</v>
+        <v>45735</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>6.76</v>
+        <v>2.13</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -4134,15 +4134,15 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>45734</v>
+        <v>45737</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>12.27</v>
+        <v>14.45</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -4152,87 +4152,87 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>45735</v>
+        <v>45738</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>6.5</v>
+        <v>97.02</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>45735</v>
+        <v>45738</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>14.64</v>
+        <v>89.06</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>45735</v>
+        <v>45738</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>6.61</v>
+        <v>91.87</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>45735</v>
+        <v>45738</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>2.21</v>
+        <v>92.08</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>45736</v>
+        <v>45738</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>12.23</v>
+        <v>17.8</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -4246,11 +4246,11 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>15.2</v>
+        <v>3.54</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -4260,25 +4260,25 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>45738</v>
+        <v>45739</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>84.04000000000001</v>
+        <v>84.75</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>45738</v>
+        <v>45739</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>11.52</v>
+        <v>16.59</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>45739</v>
+        <v>45740</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>19.4</v>
+        <v>17.52</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -4314,33 +4314,33 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>45739</v>
+        <v>45740</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>6.21</v>
+        <v>89.47</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>45739</v>
+        <v>45740</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>3.86</v>
+        <v>0.63</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>45739</v>
+        <v>45740</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>16.81</v>
+        <v>19.02</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -4372,11 +4372,11 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>88.95</v>
+        <v>3.65</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -4386,15 +4386,15 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>45740</v>
+        <v>45741</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>82.09999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>45740</v>
+        <v>45741</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>12.49</v>
+        <v>0.12</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -4422,19 +4422,19 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>45740</v>
+        <v>45741</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>8.1</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -4444,11 +4444,11 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>7.84</v>
+        <v>5.85</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -4458,15 +4458,15 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>45741</v>
+        <v>45742</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>15.41</v>
+        <v>9.91</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>45742</v>
+        <v>45744</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -4484,25 +4484,25 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>7.2</v>
+        <v>86.23</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>45742</v>
+        <v>45744</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>1.74</v>
+        <v>4.05</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -4512,19 +4512,19 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>86.52</v>
+        <v>96.88</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -4534,11 +4534,11 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>14.18</v>
+        <v>15.85</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -4556,11 +4556,11 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>14.12</v>
+        <v>97.02</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -4570,11 +4570,11 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>6.21</v>
+        <v>17.04</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -4588,11 +4588,11 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>3.09</v>
+        <v>9.73</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -4606,11 +4606,11 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>98.05</v>
+        <v>17.51</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -4620,15 +4620,15 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>45745</v>
+        <v>45746</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>6.79</v>
+        <v>5.85</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>45745</v>
+        <v>45746</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>8.26</v>
+        <v>2.66</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -4656,15 +4656,15 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>45746</v>
+        <v>45747</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>1.09</v>
+        <v>5.09</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -4674,15 +4674,15 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>45746</v>
+        <v>45747</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>4.94</v>
+        <v>19.52</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -4692,51 +4692,51 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>45746</v>
+        <v>45747</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>5.26</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>45746</v>
+        <v>45748</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>5.97</v>
+        <v>90.14</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>4.15</v>
+        <v>6.37</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -4746,15 +4746,15 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>14.47</v>
+        <v>2.66</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -4764,15 +4764,15 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>45747</v>
+        <v>45749</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>10.25</v>
+        <v>10.43</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -4782,15 +4782,15 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>45748</v>
+        <v>45750</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>92.15000000000001</v>
+        <v>7.68</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -4800,33 +4800,33 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>45748</v>
+        <v>45750</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>3.15</v>
+        <v>91.81</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>45748</v>
+        <v>45751</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>94.15000000000001</v>
+        <v>9.15</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>45749</v>
+        <v>45751</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>16.68</v>
+        <v>3.76</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -4854,15 +4854,15 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>45749</v>
+        <v>45751</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>10.4</v>
+        <v>1.25</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -4872,15 +4872,15 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>45749</v>
+        <v>45751</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>81.7</v>
+        <v>13.73</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -4890,15 +4890,15 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>45750</v>
+        <v>45752</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>12.24</v>
+        <v>5.72</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -4908,15 +4908,15 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>45750</v>
+        <v>45752</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>90.43000000000001</v>
+        <v>13.86</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>45751</v>
+        <v>45753</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>6.01</v>
+        <v>13.3</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -4944,15 +4944,15 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>45751</v>
+        <v>45753</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>17.94</v>
+        <v>8.56</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -4962,15 +4962,15 @@
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>45751</v>
+        <v>45753</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>18.48</v>
+        <v>17.58</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -4980,15 +4980,15 @@
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
-        <v>45752</v>
+        <v>45753</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>12.23</v>
+        <v>4.93</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -4998,15 +4998,15 @@
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>45753</v>
+        <v>45754</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>90.70999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -5020,11 +5020,11 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>17.44</v>
+        <v>4.83</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>15.6</v>
+        <v>15.15</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>7.08</v>
+        <v>7.42</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>86.95</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -5092,11 +5092,11 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>11</v>
+        <v>19.77</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -5106,15 +5106,15 @@
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
-        <v>45756</v>
+        <v>45755</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>10.55</v>
+        <v>14.63</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -5128,11 +5128,11 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>98.79000000000001</v>
+        <v>19.38</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -5146,11 +5146,11 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>94.98999999999999</v>
+        <v>7.43</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -5164,11 +5164,11 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>3.09</v>
+        <v>4.45</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -5178,19 +5178,19 @@
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>45756</v>
+        <v>45757</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>3.25</v>
+        <v>81.84</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -5200,11 +5200,11 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>10.6</v>
+        <v>6.15</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -5218,11 +5218,11 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>2.6</v>
+        <v>3.62</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -5232,15 +5232,15 @@
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>45757</v>
+        <v>45758</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>9.039999999999999</v>
+        <v>15.33</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -5254,11 +5254,11 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>18.97</v>
+        <v>13.74</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -5272,11 +5272,11 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>3.01</v>
+        <v>14.31</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -5290,11 +5290,11 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>11.18</v>
+        <v>0.63</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>45758</v>
+        <v>45759</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>10.29</v>
+        <v>9.59</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>45758</v>
+        <v>45760</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -5330,17 +5330,17 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>16.68</v>
+        <v>81.34</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>45759</v>
+        <v>45760</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>6.52</v>
+        <v>17.45</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>45759</v>
+        <v>45760</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>15.4</v>
+        <v>1.33</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>45759</v>
+        <v>45760</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -5384,17 +5384,17 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>2.61</v>
+        <v>89.95</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>45759</v>
+        <v>45760</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>1.05</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -5412,15 +5412,15 @@
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>45760</v>
+        <v>45761</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>6.02</v>
+        <v>14.64</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -5430,15 +5430,15 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>45760</v>
+        <v>45761</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>4.51</v>
+        <v>15.31</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -5448,15 +5448,15 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>45760</v>
+        <v>45761</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>82.87</v>
+        <v>0.73</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -5466,15 +5466,15 @@
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>45762</v>
+        <v>45761</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>0.8100000000000001</v>
+        <v>4.05</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -5484,15 +5484,15 @@
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>45763</v>
+        <v>45762</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>18.32</v>
+        <v>11.84</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -5502,15 +5502,15 @@
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>45764</v>
+        <v>45762</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>19.1</v>
+        <v>5.84</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>45764</v>
+        <v>45762</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>14.69</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -5538,15 +5538,15 @@
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>45764</v>
+        <v>45762</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>15.41</v>
+        <v>6.17</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>45764</v>
+        <v>45763</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>8.85</v>
+        <v>17.2</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>45765</v>
+        <v>45763</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -5582,25 +5582,25 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>11.13</v>
+        <v>89.12</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>45765</v>
+        <v>45763</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>12.49</v>
+        <v>7.09</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -5610,15 +5610,15 @@
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>45765</v>
+        <v>45763</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>14.23</v>
+        <v>13.3</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -5628,15 +5628,15 @@
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>45766</v>
+        <v>45764</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>88.73999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -5646,15 +5646,15 @@
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>45766</v>
+        <v>45764</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>14.23</v>
+        <v>19.46</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -5664,15 +5664,15 @@
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>45766</v>
+        <v>45764</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>1.92</v>
+        <v>15.39</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>45766</v>
+        <v>45765</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>13.19</v>
+        <v>14.86</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>45767</v>
+        <v>45765</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>94.15000000000001</v>
+        <v>1.36</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -5718,15 +5718,15 @@
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>45767</v>
+        <v>45766</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>16.26</v>
+        <v>4.93</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -5736,15 +5736,15 @@
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>45767</v>
+        <v>45766</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>3.31</v>
+        <v>3.83</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -5754,15 +5754,15 @@
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>45769</v>
+        <v>45767</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>11.63</v>
+        <v>4.98</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -5772,15 +5772,15 @@
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>45769</v>
+        <v>45767</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>7.92</v>
+        <v>18.33</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -5790,15 +5790,15 @@
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>45769</v>
+        <v>45767</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>11.17</v>
+        <v>9.44</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>45770</v>
+        <v>45767</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>94.81999999999999</v>
+        <v>4.96</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -5826,15 +5826,15 @@
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>45770</v>
+        <v>45767</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>16.61</v>
+        <v>18.33</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -5844,15 +5844,15 @@
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>45770</v>
+        <v>45767</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>15.17</v>
+        <v>7.45</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>45770</v>
+        <v>45768</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
@@ -5870,25 +5870,25 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>7.3</v>
+        <v>96.11</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
-        <v>45770</v>
+        <v>45768</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>0.01</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
-        <v>45771</v>
+        <v>45768</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>97.70999999999999</v>
+        <v>18.74</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -5916,15 +5916,15 @@
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
-        <v>45771</v>
+        <v>45768</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>9.859999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -5934,15 +5934,15 @@
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
-        <v>45771</v>
+        <v>45769</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>92.97</v>
+        <v>14.89</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -5952,15 +5952,15 @@
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
-        <v>45771</v>
+        <v>45769</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>2.6</v>
+        <v>13.74</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
-        <v>45772</v>
+        <v>45769</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>10.93</v>
+        <v>19.35</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -5988,15 +5988,15 @@
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
-        <v>45772</v>
+        <v>45769</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>11.42</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -6006,15 +6006,15 @@
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
-        <v>45772</v>
+        <v>45769</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>7.95</v>
+        <v>9.56</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -6024,25 +6024,25 @@
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
-        <v>45772</v>
+        <v>45769</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>80.7</v>
+        <v>83.39</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
-        <v>45772</v>
+        <v>45770</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>93.12</v>
+        <v>9.08</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -6060,15 +6060,15 @@
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
-        <v>45772</v>
+        <v>45770</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>2.21</v>
+        <v>4.45</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -6078,15 +6078,15 @@
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
-        <v>45773</v>
+        <v>45770</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>16.88</v>
+        <v>4.54</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
     </row>
     <row r="316">
       <c r="A316" s="1" t="n">
-        <v>45773</v>
+        <v>45770</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>84.34999999999999</v>
+        <v>4.93</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -6114,15 +6114,15 @@
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
-        <v>45774</v>
+        <v>45770</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>6.94</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -6132,15 +6132,15 @@
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
-        <v>45774</v>
+        <v>45770</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>7.64</v>
+        <v>9.91</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -6150,33 +6150,33 @@
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
-        <v>45775</v>
+        <v>45770</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>14.98</v>
+        <v>97.7</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
-        <v>45775</v>
+        <v>45771</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>7.44</v>
+        <v>4.83</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -6186,15 +6186,15 @@
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
-        <v>45775</v>
+        <v>45771</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>7.58</v>
+        <v>0.61</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -6204,15 +6204,15 @@
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
-        <v>45775</v>
+        <v>45771</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>4.4</v>
+        <v>3.93</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
-        <v>45776</v>
+        <v>45772</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>10.24</v>
+        <v>3.44</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -6240,15 +6240,15 @@
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
-        <v>45776</v>
+        <v>45772</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>16.18</v>
+        <v>10.97</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -6258,15 +6258,15 @@
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
-        <v>45777</v>
+        <v>45773</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>11.13</v>
+        <v>1.67</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -6276,15 +6276,15 @@
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
-        <v>45777</v>
+        <v>45773</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>17.94</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -6294,15 +6294,15 @@
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
-        <v>45777</v>
+        <v>45773</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>7.58</v>
+        <v>13.42</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -6312,15 +6312,15 @@
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
-        <v>45777</v>
+        <v>45773</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>6.43</v>
+        <v>1.67</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -6330,15 +6330,15 @@
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
-        <v>45777</v>
+        <v>45774</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>12.94</v>
+        <v>10.42</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -6348,15 +6348,15 @@
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
-        <v>45778</v>
+        <v>45774</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>8.800000000000001</v>
+        <v>15.46</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -6366,15 +6366,15 @@
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
-        <v>45778</v>
+        <v>45774</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>16.84</v>
+        <v>4.98</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -6384,15 +6384,15 @@
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
-        <v>45778</v>
+        <v>45774</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>4.07</v>
+        <v>7.17</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
-        <v>45778</v>
+        <v>45774</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>83.26000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -6420,15 +6420,15 @@
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
-        <v>45779</v>
+        <v>45775</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>19.4</v>
+        <v>3.99</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
-        <v>45779</v>
+        <v>45775</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
@@ -6446,25 +6446,25 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>80.12</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
-        <v>45779</v>
+        <v>45776</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>97.92</v>
+        <v>5.26</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
-        <v>45779</v>
+        <v>45776</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>8.94</v>
+        <v>15.89</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
-        <v>45779</v>
+        <v>45776</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>5.61</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -6510,15 +6510,15 @@
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
-        <v>45780</v>
+        <v>45776</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>13.3</v>
+        <v>4.59</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -6528,15 +6528,15 @@
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
-        <v>45781</v>
+        <v>45776</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>81.22</v>
+        <v>9.77</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -6546,15 +6546,15 @@
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
-        <v>45781</v>
+        <v>45778</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>18.32</v>
+        <v>3.2</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -6564,15 +6564,15 @@
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
-        <v>45781</v>
+        <v>45778</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>9.859999999999999</v>
+        <v>13.23</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
-        <v>45782</v>
+        <v>45778</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>12.23</v>
+        <v>14.48</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -6600,15 +6600,15 @@
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
-        <v>45782</v>
+        <v>45778</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>3.64</v>
+        <v>9.44</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -6618,15 +6618,15 @@
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
-        <v>45782</v>
+        <v>45778</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>12.06</v>
+        <v>6.13</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -6636,25 +6636,25 @@
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
-        <v>45782</v>
+        <v>45780</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>81.22</v>
+        <v>80.31</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
-        <v>45783</v>
+        <v>45780</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>12.36</v>
+        <v>9.56</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -6672,15 +6672,15 @@
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
-        <v>45783</v>
+        <v>45781</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>18.58</v>
+        <v>5.85</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
-        <v>45783</v>
+        <v>45781</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
@@ -6698,25 +6698,25 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>87.84</v>
+        <v>99.3</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
-        <v>45784</v>
+        <v>45781</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>14.69</v>
+        <v>5.74</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
-        <v>45784</v>
+        <v>45781</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>15.07</v>
+        <v>7.85</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -6744,15 +6744,15 @@
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
-        <v>45785</v>
+        <v>45782</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>10.24</v>
+        <v>17.51</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -6762,15 +6762,15 @@
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
-        <v>45785</v>
+        <v>45783</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>17.95</v>
+        <v>16.38</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -6780,15 +6780,15 @@
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
-        <v>45785</v>
+        <v>45783</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>16.89</v>
+        <v>1.62</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -6798,15 +6798,15 @@
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
-        <v>45786</v>
+        <v>45783</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>95.38</v>
+        <v>18.33</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -6816,15 +6816,15 @@
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
-        <v>45787</v>
+        <v>45783</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>6.27</v>
+        <v>19.73</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
-        <v>45787</v>
+        <v>45783</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>18.47</v>
+        <v>10.3</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -6852,15 +6852,15 @@
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
-        <v>45788</v>
+        <v>45784</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>10.25</v>
+        <v>1.55</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
-        <v>45788</v>
+        <v>45784</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>95.81999999999999</v>
+        <v>14.24</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -6888,15 +6888,15 @@
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
-        <v>45790</v>
+        <v>45785</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>6.88</v>
+        <v>16.38</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -6906,15 +6906,15 @@
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
-        <v>45790</v>
+        <v>45785</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>6.97</v>
+        <v>15.46</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
-        <v>45790</v>
+        <v>45785</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>6.52</v>
+        <v>7.01</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -6942,15 +6942,15 @@
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
-        <v>45790</v>
+        <v>45785</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>7.2</v>
+        <v>14.16</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -6960,15 +6960,15 @@
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
-        <v>45791</v>
+        <v>45785</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>4.07</v>
+        <v>2.37</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -6978,15 +6978,15 @@
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
-        <v>45791</v>
+        <v>45785</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>14.14</v>
+        <v>0.58</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
-        <v>45792</v>
+        <v>45785</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>15.24</v>
+        <v>0.93</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -7014,33 +7014,33 @@
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
-        <v>45792</v>
+        <v>45786</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>17.6</v>
+        <v>99.44</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
-        <v>45792</v>
+        <v>45787</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>16.84</v>
+        <v>13.51</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -7050,15 +7050,15 @@
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
-        <v>45794</v>
+        <v>45787</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>19.85</v>
+        <v>2.49</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -7068,15 +7068,15 @@
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
-        <v>45794</v>
+        <v>45788</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>0.65</v>
+        <v>19.77</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -7086,15 +7086,15 @@
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
-        <v>45794</v>
+        <v>45789</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>12.73</v>
+        <v>10.97</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -7104,15 +7104,15 @@
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
-        <v>45795</v>
+        <v>45789</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>91.54000000000001</v>
+        <v>10.43</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -7122,15 +7122,15 @@
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
-        <v>45796</v>
+        <v>45789</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>13.36</v>
+        <v>13.5</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -7140,15 +7140,15 @@
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
-        <v>45796</v>
+        <v>45789</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>94.3</v>
+        <v>2.33</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -7158,15 +7158,15 @@
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
-        <v>45796</v>
+        <v>45789</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>16.36</v>
+        <v>1.23</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -7176,15 +7176,15 @@
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
-        <v>45796</v>
+        <v>45790</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>18.91</v>
+        <v>15.66</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -7194,15 +7194,15 @@
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
-        <v>45796</v>
+        <v>45790</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>3.25</v>
+        <v>13.48</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -7212,15 +7212,15 @@
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
-        <v>45797</v>
+        <v>45790</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>15.06</v>
+        <v>12.31</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -7230,15 +7230,15 @@
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
-        <v>45797</v>
+        <v>45791</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>15.17</v>
+        <v>13.31</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -7248,15 +7248,15 @@
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
-        <v>45798</v>
+        <v>45793</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>95.81999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -7266,25 +7266,25 @@
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
-        <v>45798</v>
+        <v>45795</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>0.16</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
-        <v>45799</v>
+        <v>45795</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>1.92</v>
+        <v>17.04</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -7302,15 +7302,15 @@
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
-        <v>45799</v>
+        <v>45796</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>12.49</v>
+        <v>1.65</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -7320,15 +7320,15 @@
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
-        <v>45800</v>
+        <v>45796</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>81.55</v>
+        <v>8.19</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
-        <v>45800</v>
+        <v>45796</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
@@ -7346,25 +7346,25 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>18.81</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
-        <v>45801</v>
+        <v>45796</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>90.03</v>
+        <v>3.44</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -7374,15 +7374,15 @@
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
-        <v>45801</v>
+        <v>45797</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>86.70999999999999</v>
+        <v>0.42</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -7392,15 +7392,15 @@
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
-        <v>45802</v>
+        <v>45797</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>14.19</v>
+        <v>14.63</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -7410,15 +7410,15 @@
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
-        <v>45802</v>
+        <v>45797</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>7.08</v>
+        <v>19.61</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -7428,33 +7428,33 @@
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
-        <v>45802</v>
+        <v>45797</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>11</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
-        <v>45802</v>
+        <v>45798</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>2.79</v>
+        <v>1.62</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
-        <v>45802</v>
+        <v>45798</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>16.81</v>
+        <v>15.19</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
-        <v>45803</v>
+        <v>45799</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>6.88</v>
+        <v>4.68</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
-        <v>45804</v>
+        <v>45799</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>11.55</v>
+        <v>17.26</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -7518,15 +7518,15 @@
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
-        <v>45804</v>
+        <v>45799</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>9.859999999999999</v>
+        <v>7.01</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -7536,33 +7536,33 @@
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
-        <v>45804</v>
+        <v>45799</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>10.61</v>
+        <v>97.02</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
-        <v>45805</v>
+        <v>45800</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>3.08</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -7572,33 +7572,33 @@
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
-        <v>45805</v>
+        <v>45800</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>12.17</v>
+        <v>99.44</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
-        <v>45806</v>
+        <v>45800</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>7.64</v>
+        <v>5.2</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -7608,15 +7608,15 @@
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
-        <v>45806</v>
+        <v>45801</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>16.98</v>
+        <v>13.5</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -7626,15 +7626,15 @@
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
-        <v>45806</v>
+        <v>45801</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>9.140000000000001</v>
+        <v>2.03</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -7644,105 +7644,105 @@
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
-        <v>45807</v>
+        <v>45802</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>83.98</v>
+        <v>2.78</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
-        <v>45808</v>
+        <v>45802</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>11.94</v>
+        <v>19.9</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
-        <v>45808</v>
+        <v>45802</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>8.800000000000001</v>
+        <v>5.91</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
-        <v>45808</v>
+        <v>45803</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C405" t="n">
-        <v>14.12</v>
+        <v>9.49</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
-        <v>45808</v>
+        <v>45803</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>6.97</v>
+        <v>2.32</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
-        <v>45808</v>
+        <v>45804</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>10.14</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -7752,15 +7752,15 @@
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
-        <v>45809</v>
+        <v>45805</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>9.66</v>
+        <v>8.98</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -7770,61 +7770,61 @@
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
-        <v>45810</v>
+        <v>45805</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>0.47</v>
+        <v>5.81</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
-        <v>45810</v>
+        <v>45805</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>14.18</v>
+        <v>15.46</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
-        <v>45810</v>
+        <v>45805</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>12.23</v>
+        <v>15.9</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
-        <v>45810</v>
+        <v>45805</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
@@ -7832,53 +7832,53 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>81.23999999999999</v>
+        <v>3.61</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
-        <v>45810</v>
+        <v>45805</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>17.76</v>
+        <v>13.92</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
-        <v>45810</v>
+        <v>45805</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>6.52</v>
+        <v>3.1</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
-        <v>45811</v>
+        <v>45806</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
@@ -7886,35 +7886,35 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>19.47</v>
+        <v>15.33</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="1" t="n">
-        <v>45811</v>
+        <v>45807</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>14.19</v>
+        <v>10.86</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="1" t="n">
-        <v>45811</v>
+        <v>45807</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
@@ -7922,169 +7922,169 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>16.1</v>
+        <v>15.37</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="1" t="n">
-        <v>45811</v>
+        <v>45807</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>9.279999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="1" t="n">
-        <v>45811</v>
+        <v>45807</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>11.67</v>
+        <v>0.93</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="1" t="n">
-        <v>45811</v>
+        <v>45807</v>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>3.64</v>
+        <v>3.86</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="1" t="n">
-        <v>45811</v>
+        <v>45808</v>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>84.12</v>
+        <v>13.86</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="1" t="n">
-        <v>45811</v>
+        <v>45808</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>6.42</v>
+        <v>4.93</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="1" t="n">
-        <v>45812</v>
+        <v>45808</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C423" t="n">
-        <v>13.36</v>
+        <v>17.43</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="1" t="n">
-        <v>45812</v>
+        <v>45808</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>14.98</v>
+        <v>2.33</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="1" t="n">
-        <v>45812</v>
+        <v>45809</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>98.05</v>
+        <v>17.65</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="1" t="n">
-        <v>45812</v>
+        <v>45809</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>17.2</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
     </row>
     <row r="427">
       <c r="A427" s="1" t="n">
-        <v>45812</v>
+        <v>45810</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
@@ -8102,107 +8102,107 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>16.54</v>
+        <v>4.05</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="1" t="n">
-        <v>45813</v>
+        <v>45810</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>97.11</v>
+        <v>5.09</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="1" t="n">
-        <v>45813</v>
+        <v>45811</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>9.18</v>
+        <v>2.33</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="1" t="n">
-        <v>45814</v>
+        <v>45812</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C430" t="n">
-        <v>14.73</v>
+        <v>8.07</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="1" t="n">
-        <v>45814</v>
+        <v>45812</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>89.84</v>
+        <v>9.58</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="1" t="n">
-        <v>45814</v>
+        <v>45812</v>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C432" t="n">
-        <v>16.68</v>
+        <v>7.51</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="1" t="n">
-        <v>45814</v>
+        <v>45812</v>
       </c>
       <c r="B433" t="inlineStr">
         <is>
@@ -8210,35 +8210,35 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>19.47</v>
+        <v>19.09</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="1" t="n">
-        <v>45815</v>
+        <v>45813</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>12.49</v>
+        <v>3.04</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="1" t="n">
-        <v>45815</v>
+        <v>45813</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>7.92</v>
+        <v>91.81</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
     </row>
     <row r="436">
       <c r="A436" s="1" t="n">
-        <v>45816</v>
+        <v>45813</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
@@ -8264,17 +8264,17 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>11.55</v>
+        <v>13.23</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="1" t="n">
-        <v>45816</v>
+        <v>45813</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
@@ -8282,35 +8282,35 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>19</v>
+        <v>2.61</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="1" t="n">
-        <v>45816</v>
+        <v>45814</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>10.65</v>
+        <v>15.81</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="1" t="n">
-        <v>45817</v>
+        <v>45814</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
@@ -8318,161 +8318,161 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>17.95</v>
+        <v>13.49</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="1" t="n">
-        <v>45817</v>
+        <v>45815</v>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>16.54</v>
+        <v>14.01</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="1" t="n">
-        <v>45817</v>
+        <v>45816</v>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C441" t="n">
-        <v>81.95</v>
+        <v>15.46</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="1" t="n">
-        <v>45818</v>
+        <v>45816</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C442" t="n">
-        <v>5.51</v>
+        <v>13.57</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="1" t="n">
-        <v>45818</v>
+        <v>45816</v>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C443" t="n">
-        <v>18.92</v>
+        <v>4.97</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="1" t="n">
-        <v>45818</v>
+        <v>45817</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C444" t="n">
-        <v>0.05</v>
+        <v>10.93</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="1" t="n">
-        <v>45819</v>
+        <v>45817</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>88.95</v>
+        <v>5.74</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="1" t="n">
-        <v>45820</v>
+        <v>45818</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>19.1</v>
+        <v>0.34</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="1" t="n">
-        <v>45820</v>
+        <v>45818</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C447" t="n">
-        <v>2.52</v>
+        <v>7.59</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="1" t="n">
-        <v>45821</v>
+        <v>45818</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
@@ -8480,79 +8480,79 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>92.81999999999999</v>
+        <v>19.71</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="1" t="n">
-        <v>45822</v>
+        <v>45819</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C449" t="n">
-        <v>8.800000000000001</v>
+        <v>10.42</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="1" t="n">
-        <v>45822</v>
+        <v>45819</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C450" t="n">
-        <v>4.02</v>
+        <v>10.97</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="1" t="n">
-        <v>45822</v>
+        <v>45819</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>10.28</v>
+        <v>16.59</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="1" t="n">
-        <v>45822</v>
+        <v>45820</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C452" t="n">
-        <v>94.81999999999999</v>
+        <v>97.69</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -8562,69 +8562,69 @@
     </row>
     <row r="453">
       <c r="A453" s="1" t="n">
-        <v>45822</v>
+        <v>45820</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C453" t="n">
-        <v>11.77</v>
+        <v>19.77</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="1" t="n">
-        <v>45822</v>
+        <v>45820</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>82.09999999999999</v>
+        <v>2.53</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="1" t="n">
-        <v>45823</v>
+        <v>45820</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>9.43</v>
+        <v>15.37</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="1" t="n">
-        <v>45823</v>
+        <v>45820</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C456" t="n">
-        <v>10.14</v>
+        <v>99.77</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -8634,61 +8634,61 @@
     </row>
     <row r="457">
       <c r="A457" s="1" t="n">
-        <v>45823</v>
+        <v>45820</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>5.58</v>
+        <v>2.25</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="1" t="n">
-        <v>45824</v>
+        <v>45820</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>12.82</v>
+        <v>13.45</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="1" t="n">
-        <v>45825</v>
+        <v>45820</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>4.77</v>
+        <v>17.02</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="1" t="n">
-        <v>45825</v>
+        <v>45821</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -8696,17 +8696,17 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>3.03</v>
+        <v>18.15</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="1" t="n">
-        <v>45825</v>
+        <v>45821</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>16.45</v>
+        <v>82.69</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -8724,33 +8724,33 @@
     </row>
     <row r="462">
       <c r="A462" s="1" t="n">
-        <v>45825</v>
+        <v>45822</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>12.06</v>
+        <v>0.61</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="1" t="n">
-        <v>45826</v>
+        <v>45824</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>4.02</v>
+        <v>80.88</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -8760,15 +8760,15 @@
     </row>
     <row r="464">
       <c r="A464" s="1" t="n">
-        <v>45826</v>
+        <v>45824</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C464" t="n">
-        <v>16.89</v>
+        <v>89.06</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -8778,19 +8778,19 @@
     </row>
     <row r="465">
       <c r="A465" s="1" t="n">
-        <v>45826</v>
+        <v>45824</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>2.95</v>
+        <v>5.95</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8800,15 +8800,15 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>16.84</v>
+        <v>6.24</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8818,33 +8818,33 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>0.29</v>
+        <v>17.07</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="1" t="n">
-        <v>45828</v>
+        <v>45827</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C468" t="n">
-        <v>95.28</v>
+        <v>19.18</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8854,15 +8854,15 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>16.97</v>
+        <v>3.86</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8876,11 +8876,11 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>92.97</v>
+        <v>4.05</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8890,21 +8890,21 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>3.79</v>
+        <v>8.02</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="1" t="n">
-        <v>45829</v>
+        <v>45828</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
@@ -8912,17 +8912,17 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>2.07</v>
+        <v>6.53</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="1" t="n">
-        <v>45830</v>
+        <v>45829</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>12.05</v>
+        <v>96.77</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -8940,43 +8940,43 @@
     </row>
     <row r="474">
       <c r="A474" s="1" t="n">
-        <v>45830</v>
+        <v>45829</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C474" t="n">
-        <v>15.4</v>
+        <v>10.33</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="1" t="n">
-        <v>45830</v>
+        <v>45829</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C475" t="n">
-        <v>9.93</v>
+        <v>13.48</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="1" t="n">
-        <v>45831</v>
+        <v>45829</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
@@ -8984,35 +8984,35 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>18.91</v>
+        <v>5.84</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="1" t="n">
-        <v>45832</v>
+        <v>45829</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>4.71</v>
+        <v>4.87</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="1" t="n">
-        <v>45833</v>
+        <v>45830</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>19.4</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
     </row>
     <row r="479">
       <c r="A479" s="1" t="n">
-        <v>45833</v>
+        <v>45830</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
@@ -9038,53 +9038,53 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>4.07</v>
+        <v>13.3</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="1" t="n">
-        <v>45834</v>
+        <v>45830</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>2.95</v>
+        <v>12.95</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="1" t="n">
-        <v>45834</v>
+        <v>45831</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Gowning Room</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>18.47</v>
+        <v>5.47</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="1" t="n">
-        <v>45834</v>
+        <v>45831</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
@@ -9092,25 +9092,25 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>15.06</v>
+        <v>13.89</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="1" t="n">
-        <v>45835</v>
+        <v>45832</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C483" t="n">
-        <v>3.38</v>
+        <v>96.11</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -9120,15 +9120,15 @@
     </row>
     <row r="484">
       <c r="A484" s="1" t="n">
-        <v>45836</v>
+        <v>45832</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>7.44</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -9138,79 +9138,79 @@
     </row>
     <row r="485">
       <c r="A485" s="1" t="n">
-        <v>45836</v>
+        <v>45832</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>4.84</v>
+        <v>4.66</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="1" t="n">
-        <v>45836</v>
+        <v>45832</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Prep Area</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>13.52</v>
+        <v>13.3</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="1" t="n">
-        <v>45836</v>
+        <v>45833</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>4.14</v>
+        <v>1.25</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="1" t="n">
-        <v>45836</v>
+        <v>45834</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>12.82</v>
+        <v>14.54</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="1" t="n">
-        <v>45836</v>
+        <v>45834</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
@@ -9218,25 +9218,25 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>13.8</v>
+        <v>3.86</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="1" t="n">
-        <v>45836</v>
+        <v>45834</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C490" t="n">
-        <v>13.19</v>
+        <v>93.59</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
     </row>
     <row r="491">
       <c r="A491" s="1" t="n">
-        <v>45836</v>
+        <v>45834</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
@@ -9254,17 +9254,17 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>11.96</v>
+        <v>19.52</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="1" t="n">
-        <v>45837</v>
+        <v>45834</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
@@ -9272,25 +9272,25 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>83.41</v>
+        <v>4.66</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="1" t="n">
-        <v>45837</v>
+        <v>45834</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C493" t="n">
-        <v>10.13</v>
+        <v>81.84</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -9300,61 +9300,61 @@
     </row>
     <row r="494">
       <c r="A494" s="1" t="n">
-        <v>45837</v>
+        <v>45835</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C494" t="n">
-        <v>10.7</v>
+        <v>0.58</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="1" t="n">
-        <v>45837</v>
+        <v>45835</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Filling Room</t>
+          <t>Corridor A</t>
         </is>
       </c>
       <c r="C495" t="n">
-        <v>7.3</v>
+        <v>11.54</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="1" t="n">
-        <v>45837</v>
+        <v>45836</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Gowning Room</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C496" t="n">
-        <v>16.81</v>
+        <v>4.97</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="1" t="n">
-        <v>45838</v>
+        <v>45836</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>2.84</v>
+        <v>89.47</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
     </row>
     <row r="498">
       <c r="A498" s="1" t="n">
-        <v>45838</v>
+        <v>45836</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
@@ -9380,29 +9380,29 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>9.539999999999999</v>
+        <v>2.25</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="1" t="n">
-        <v>45838</v>
+        <v>45836</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Prep Area</t>
         </is>
       </c>
       <c r="C499" t="n">
-        <v>10.31</v>
+        <v>16.32</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>5.05</v>
+        <v>87.7</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -9430,15 +9430,15 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Corridor A</t>
+          <t>Filling Room</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>16.88</v>
+        <v>11.84</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
